--- a/data/graduate_jobs.xlsx
+++ b/data/graduate_jobs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\IE FYP term2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD38B6A-EF8A-4CE6-821F-B5B470B4A009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B8CC45-0D8F-4789-86AF-A0E254E1ED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="4080" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23088" yWindow="4188" windowWidth="11664" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="1007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="1251">
   <si>
     <t>job_title</t>
-  </si>
-  <si>
-    <t>company_name</t>
   </si>
   <si>
     <t>location</t>
@@ -3061,6 +3058,772 @@
   </si>
   <si>
     <t>DR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Biomedical Engineer (Medical Device)</t>
+  </si>
+  <si>
+    <t>Advanced Semiconductor Integrations Limited</t>
+  </si>
+  <si>
+    <t>Sha Tin (Science Park)</t>
+  </si>
+  <si>
+    <t>admin@advsemint.com</t>
+  </si>
+  <si>
+    <t>Medical Device / EE</t>
+  </si>
+  <si>
+    <t>Full-time</t>
+  </si>
+  <si>
+    <t>BME/EE degree, Verification &amp; Validation (V&amp;V), Risk analysis (FMEA), Tech documentation</t>
+  </si>
+  <si>
+    <t>FDA design controls, Neuro-stimulation device design, Low-power Analog IC knowledge</t>
+  </si>
+  <si>
+    <t>Design and develop Class-3 implantable neuro-stimulation devices. Handle V&amp;V testing, FMEA hazards mitigation, and document quality systems (BOMs, protocols).</t>
+  </si>
+  <si>
+    <t>Innovative start-up environment, mentorship from 30+ years industry veterans, exposure to global semiconductor &amp; medical markets.</t>
+  </si>
+  <si>
+    <t>DS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Electronic Engineer (Digital ASIC/FPGA)</t>
+  </si>
+  <si>
+    <t>IC Design / EE</t>
+  </si>
+  <si>
+    <t>EE/Physics degree (BSc/MSc/PhD), Verilog, Logic design, Circuit simulation</t>
+  </si>
+  <si>
+    <t>Full IC development flow, FPGA prototyping, Mixed-signal design, ATE development</t>
+  </si>
+  <si>
+    <t>Participate in the full ASIC development cycle for medical, automotive, and consumer electronics. Involves FPGA prototyping, pre/post-layout simulation, silicon bring-up, and evaluation.</t>
+  </si>
+  <si>
+    <t>Involvement in complete design-to-production journey, work with industry veterans, competitive benefits/bonuses, 100% Science Park based.</t>
+  </si>
+  <si>
+    <t>DT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Firmware Engineer (Medical Device)</t>
+  </si>
+  <si>
+    <t>Embedded Systems / BLE</t>
+  </si>
+  <si>
+    <t>CE/EE degree, ARM Microcontrollers, C programming, Mobile App dev</t>
+  </si>
+  <si>
+    <t>BLE protocols, Low-power management, Circuit schematics reading, Oscilloscope/Logic analyzer</t>
+  </si>
+  <si>
+    <t>Develop firmware for neurostimulation devices using ARM MCUs. Design BLE communication protocols and mobile control apps. Perform low-power optimization and hardware-firmware interfacing.</t>
+  </si>
+  <si>
+    <t>Work in a high-impact medical start-up, gain experience in regulated med-tech, attractive benefits and Science Park environment.</t>
+  </si>
+  <si>
+    <t>DU</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fund Operation Analyst/Associate</t>
+  </si>
+  <si>
+    <t>WizardQuant LLC</t>
+  </si>
+  <si>
+    <t>Kowloon Bay, Hong Kong</t>
+  </si>
+  <si>
+    <t>Quant Hedge Fund / Operations</t>
+  </si>
+  <si>
+    <t>Bachelor in Finance/Accounting, Analytical sense, Eng &amp; Mandarin</t>
+  </si>
+  <si>
+    <t>Hedge fund ops exp, Audit coordination, Cash management</t>
+  </si>
+  <si>
+    <t>Responsible for NAV reviewing, reconciliation, and fund administration. Liaise with auditors, support financial filing for new products, and assist in risk reporting/newsletters.</t>
+  </si>
+  <si>
+    <t>Exposure to a premier global quant team, dynamic innovation culture, cross-border office presence (NYC/HK/Mainland).</t>
+  </si>
+  <si>
+    <t>DV</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Trader</t>
+  </si>
+  <si>
+    <t>Quantitative Finance</t>
+  </si>
+  <si>
+    <t>Bachelor/Master in Math/CS/Finance, Python, Solid Math</t>
+  </si>
+  <si>
+    <t>Order flow analysis, Slippage analysis, Risk escalation</t>
+  </si>
+  <si>
+    <t>Manage and monitor automated trading systems. Respond to market anomalies, conduct pre/post-trade analysis (slippage, risk), and collaborate with researchers to optimize execution strategies.</t>
+  </si>
+  <si>
+    <t>High-stakes frontline trading experience, exposure to global markets (HK/US/Mainland), collaborative innovation culture.</t>
+  </si>
+  <si>
+    <t>DW</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Engineer</t>
+  </si>
+  <si>
+    <t>CS Metal Internationed Limited</t>
+  </si>
+  <si>
+    <t>Various (HK, Dongguan, Mexico)</t>
+  </si>
+  <si>
+    <t>info@cs-metal.ltd</t>
+  </si>
+  <si>
+    <t>Manufacturing / IE</t>
+  </si>
+  <si>
+    <t>BEng in Mechanical/Industrial/Manufacturing, CAD, Cantonese/Mandarin/Eng</t>
+  </si>
+  <si>
+    <t>FMEA, Control Plan, NPI, Lean Manufacturing</t>
+  </si>
+  <si>
+    <t>Optimize metal fabrication (welding, stamping). Design processes, troubleshoot equipment, and analyze production data for cost reduction. Support new product development (NPI).</t>
+  </si>
+  <si>
+    <t>Monthly $30,000 - $35,000, Global exposure (Mexico/Dongguan), 40+ years industry heritage.</t>
+  </si>
+  <si>
+    <t>DX</t>
+  </si>
+  <si>
+    <t>DX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Graduate Engineer</t>
+  </si>
+  <si>
+    <t>中鐵建設集團有限公司 (CRCC)</t>
+  </si>
+  <si>
+    <t>Various Districts, HK</t>
+  </si>
+  <si>
+    <t>recruitment@crcghk.com</t>
+  </si>
+  <si>
+    <t>Civil / Construction</t>
+  </si>
+  <si>
+    <t>Degree in Civil/Building/Structural Eng, HKIE Scheme A eligible</t>
+  </si>
+  <si>
+    <t>Mandarin (Preferred), Site coordination, Tech submission</t>
+  </si>
+  <si>
+    <t>Assist in project operations, site engineering support, planning, and preparing technical/tender submissions. Rotational training under HKIE Scheme A standards.</t>
+  </si>
+  <si>
+    <t>Monthly $25,000 - $30,000, HKIE Scheme A Training, exposure to large-scale national infrastructure projects.</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>DY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>company_name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Engineer, Metrology &amp; Real Time Defects Analysis</t>
+  </si>
+  <si>
+    <t>Micron Semiconductor Asia</t>
+  </si>
+  <si>
+    <t>Singapore (Overseas)</t>
+  </si>
+  <si>
+    <t>chiewchingch@micron.com</t>
+  </si>
+  <si>
+    <t>Semiconductor / Yield</t>
+  </si>
+  <si>
+    <t>Engineering/Science Degree</t>
+  </si>
+  <si>
+    <t>SPC, Data Analytics, Semiconductor exp</t>
+  </si>
+  <si>
+    <t>Develop measurement recipes and apply advanced analytics to identify machinery deviations. Design experiments for defect improvement and implement SPC monitoring for tool qualification.</t>
+  </si>
+  <si>
+    <t>Monthly $29,000 - $33,000, Overseas experience, global mobility, 5 vacancies, comprehensive training.</t>
+  </si>
+  <si>
+    <t>Engineer, F10 DAST AUTOMATION</t>
+  </si>
+  <si>
+    <t>Automation / AI</t>
+  </si>
+  <si>
+    <t>Engineering Degree (EE/ME/Chem)</t>
+  </si>
+  <si>
+    <t>ASRS, AI-driven Predictive Maintenance</t>
+  </si>
+  <si>
+    <t>Support ASRS, conveyor systems, and RFID integration. Develop AI-powered digital twins for simulation. Implement AI-enabled OCR and barcode solutions for warehouse WMS integration.</t>
+  </si>
+  <si>
+    <t>Monthly $29,000 - $33,000, 10 Vacancies, Overseas career, Leading-edge AI/Automation exposure.</t>
+  </si>
+  <si>
+    <t>DZ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Manufacturing Equipment / Production Engineer</t>
+  </si>
+  <si>
+    <t>Equipment Engineering</t>
+  </si>
+  <si>
+    <t>Project Management, QMS, Hardware optimization</t>
+  </si>
+  <si>
+    <t>Own equipment maintenance schedules &amp; new tool installations. Reduce defects &amp; improve tool availability. Liaison between facilities, vendors, and shift personnel. Ensure QMS compliance.</t>
+  </si>
+  <si>
+    <t>Monthly $29,000 - $33,000, 5 Vacancies, Global career path, High-impact frontline R&amp;D role.</t>
+  </si>
+  <si>
+    <t>EA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Probe Integration Engineer</t>
+  </si>
+  <si>
+    <t>Semiconductor Test / AI</t>
+  </si>
+  <si>
+    <t>EE / ME Degree</t>
+  </si>
+  <si>
+    <t>3D CAD, Project Management</t>
+  </si>
+  <si>
+    <t>Integrate AI-assisted tools into wafer testing. Deploy first-of-a-kind Wafer Probers &amp; Probe Cards. Collaborate with global teams to implement best-known methods and perform statistical analysis on manufacturing data.</t>
+  </si>
+  <si>
+    <t>Monthly $29,000 - $33,000, 5 Vacancies, Global leadership exposure, AI enablement training.</t>
+  </si>
+  <si>
+    <t>EB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Engineer, HBM &amp; NPI</t>
+  </si>
+  <si>
+    <t>HBM / NPI / AI</t>
+  </si>
+  <si>
+    <t>JMP, Python, FMEA, DOE</t>
+  </si>
+  <si>
+    <t>Enable smooth technology transfer for HBM from R&amp;D to high-volume manufacturing. Apply DOE to accelerate learning cycles. Perform FMEA and risk assessments for NPI.</t>
+  </si>
+  <si>
+    <t>Monthly $29,000 - $33,000, 20 Vacancies, Core AI hardware exposure (HBM), International career.</t>
+  </si>
+  <si>
+    <t>EC</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Engineer, Test Solution</t>
+  </si>
+  <si>
+    <t>Chiewchingch@micron.com</t>
+  </si>
+  <si>
+    <t>SSD / Test Dev</t>
+  </si>
+  <si>
+    <t>EE / Computer Engineering</t>
+  </si>
+  <si>
+    <t>Python, Git, AI/ML concepts</t>
+  </si>
+  <si>
+    <t>Develop &amp; optimize SSD test programs for high volume manufacturing. Write scripts to automate engineering processes. Enhance test coverage &amp; debug manufacturing issues.</t>
+  </si>
+  <si>
+    <t>Monthly $29,000 - $33,000, 20 Vacancies, Overseas career, SSD technology expertise.</t>
+  </si>
+  <si>
+    <t>ED</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PDE Product Integration Engineer (PIE)</t>
+  </si>
+  <si>
+    <t>Packaging / NPI</t>
+  </si>
+  <si>
+    <t>Mechanical / Materials / EE</t>
+  </si>
+  <si>
+    <t>Yield analysis, FA methodologies</t>
+  </si>
+  <si>
+    <t>Drive NPI process through Phase Gate reviews. Coordinate new product start-up and qualification. Lead Failure Analysis (EFA/PFA) for assembly issues (warpage, shorts). Own the Product Life Cycle from NPI to EOL.</t>
+  </si>
+  <si>
+    <t>Monthly $29,000 - $33,000, 5 Vacancies, Full Product Life Cycle ownership, Advanced Packaging exposure.</t>
+  </si>
+  <si>
+    <t>EE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Process Development Engineer</t>
+  </si>
+  <si>
+    <t>Process R&amp;D / NPI</t>
+  </si>
+  <si>
+    <t>Mechanical / Chemical / Materials Eng</t>
+  </si>
+  <si>
+    <t>SPC, FMEA, Data Analysis</t>
+  </si>
+  <si>
+    <t>Owner of assembly process modules. Develop recipes for Best-In-Class yield/cost. Perform characterization to define process boundaries. Manage TRA, SPC, and FMEA for NPI. Standardize BKM recipes globally.</t>
+  </si>
+  <si>
+    <t>Monthly $29,000 - $33,000, 12 Vacancies, Global Leader exposure, Advanced Process R&amp;D.</t>
+  </si>
+  <si>
+    <t>EF</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HBM Reliability Coding Engineer</t>
+  </si>
+  <si>
+    <t>AI Memory / Software</t>
+  </si>
+  <si>
+    <t>Python, C++, EE/CS Degree</t>
+  </si>
+  <si>
+    <t>CMOS, DRAM Physics, JMP</t>
+  </si>
+  <si>
+    <t>Develop &amp; debug reliability test programs (Python/C++) for HBM. Innovate new reliability features and optimize code infrastructure. Define hardware specs and perform data-driven risk assessment.</t>
+  </si>
+  <si>
+    <t>Monthly $29,000 - $33,000, 15 Vacancies, Cutting-edge HBM reliability tech, Mentorship, Global career.</t>
+  </si>
+  <si>
+    <t>EG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HBM Manufacturing Engineer</t>
+  </si>
+  <si>
+    <t>AI Memory / Yield</t>
+  </si>
+  <si>
+    <t>EE Degree, CMOS, DRAM</t>
+  </si>
+  <si>
+    <t>Verilog, CAD, Python/JMP</t>
+  </si>
+  <si>
+    <t>Focus on HBM manufacturing test coverage and product validation. Use CAD/Verilog for circuit verification. Improve yield for DRAM and stacked dies. Resolve RMA and manufacturing test flow issues.</t>
+  </si>
+  <si>
+    <t>Monthly $30,000 - $38,000, 15 Vacancies, High-impact AI hardware role, Mentor program.</t>
+  </si>
+  <si>
+    <t>EH</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rivermap</t>
+  </si>
+  <si>
+    <t>Southern (Cyberport)</t>
+  </si>
+  <si>
+    <t>Python, SQL, MongoDB</t>
+  </si>
+  <si>
+    <t>AWS, ETL/ELT, Fin Data</t>
+  </si>
+  <si>
+    <t>Design &amp; build end-to-end data pipelines for market data. Manage AWS infrastructure. Implement AI-driven data validation &amp; anomaly detection. Collaborate with Quant &amp; Research teams.</t>
+  </si>
+  <si>
+    <t>Monthly $25k-$26k, Cyberport Incubation, AI-driven platform, exposure to Quant research.</t>
+  </si>
+  <si>
+    <t>EI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Management Trainee (BD)</t>
+  </si>
+  <si>
+    <t>Multiable</t>
+  </si>
+  <si>
+    <t>Management / BD</t>
+  </si>
+  <si>
+    <t>Numeric-sensitive, Business Insight</t>
+  </si>
+  <si>
+    <t>Accounting, HR, Ops Management</t>
+  </si>
+  <si>
+    <t>Rotational program (R&amp;D, Implementation, Dev). Assist in enterprise consultation. Perform business analysis. Possible business trips to Singapore/PRC/UK.</t>
+  </si>
+  <si>
+    <t>Monthly $23k-$27k, Leading ERP developer, Multi-city rotation, fast-track to management.</t>
+  </si>
+  <si>
+    <t>EJ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Construction AI Specialist</t>
+  </si>
+  <si>
+    <t>Ranger Construction</t>
+  </si>
+  <si>
+    <t>Wong Tai Sin</t>
+  </si>
+  <si>
+    <t>hr@ranger4s.com</t>
+  </si>
+  <si>
+    <t>AI / IoT</t>
+  </si>
+  <si>
+    <t>Python, YOLO, PyTorch</t>
+  </si>
+  <si>
+    <t>BIM (Revit), NVIDIA Jetson</t>
+  </si>
+  <si>
+    <t>Deploy CV models for PPE &amp; safety surveillance. Integrate AI with IoT hardware (smart helmets). Sync site data with Digital Twins (BIM). Automate safety audits and predictive risk analytics.</t>
+  </si>
+  <si>
+    <t>$18k - $23k, Leading edge in PropTech/ConTech, Exposure to ESG &amp; Digital Twin.</t>
+  </si>
+  <si>
+    <t>EK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI Marketing Specialist</t>
+  </si>
+  <si>
+    <t>MarTech / AI</t>
+  </si>
+  <si>
+    <t>Gemini, GPT-4, Zapier</t>
+  </si>
+  <si>
+    <t>RAG, Prompt Eng, AIO</t>
+  </si>
+  <si>
+    <t>Build AI "Content Factory" for multimodal production. Automate lead nurturing via AI agents. Transition SEO to AIO (AI Optimization). Create internal AI Playbook.</t>
+  </si>
+  <si>
+    <t>$18k - $23k, 2 Vacancies, lead the AIO revolution, high-level AI orchestration.</t>
+  </si>
+  <si>
+    <t>EL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Financial Planner</t>
+  </si>
+  <si>
+    <t>Million Golden Holding</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>Finance / Wealth</t>
+  </si>
+  <si>
+    <t>Wealth Mgmt, Risk Mgmt</t>
+  </si>
+  <si>
+    <t>Fluent Mandarin</t>
+  </si>
+  <si>
+    <t>Identify needs of HNWIs. Provide advice on investment, MPF, and retirement planning. Develop corporate solutions for firms. Maintain long-term client relationships.</t>
+  </si>
+  <si>
+    <t>Career in Private Wealth, Exposure to talent schemes (TTPS/IANG), Professional training.</t>
+  </si>
+  <si>
+    <t>EM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>App/Web/IoT</t>
+  </si>
+  <si>
+    <t>Java, Python, JS</t>
+  </si>
+  <si>
+    <t>MQTT, SQL, Git</t>
+  </si>
+  <si>
+    <t>Design software for real-time safety monitoring. Integrate IoT sensors via MQTT/REST. Develop intuitive Web/Mobile UIs. Implement safety analytics and incident reporting.</t>
+  </si>
+  <si>
+    <t>$17k - $19k, 2 Vacancies, Smart Site (SSSS) exposure, Industry 4.0 experience.</t>
+  </si>
+  <si>
+    <t>EN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Graduate Patent Engineer</t>
+  </si>
+  <si>
+    <t>LONGSUN LEAD IP</t>
+  </si>
+  <si>
+    <t>Sha Tin</t>
+  </si>
+  <si>
+    <t>mail@longsunlead.com.hk</t>
+  </si>
+  <si>
+    <t>Legal / IP</t>
+  </si>
+  <si>
+    <t>Tech Analysis, Argumentation</t>
+  </si>
+  <si>
+    <t>Master Degree</t>
+  </si>
+  <si>
+    <t>Draft patent specifications in EN/CN. Analyze technical disclosures to identify inventions. Prepare arguments for examination reports. Bridge Chinese innovation to global markets.</t>
+  </si>
+  <si>
+    <t>$20k - $30k, Systematic mentorship, Visa sponsorship (IANG/TTPS), Global IP career path.</t>
+  </si>
+  <si>
+    <t>EO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lab Assistant</t>
+  </si>
+  <si>
+    <t>NutrigeneAI</t>
+  </si>
+  <si>
+    <t>Sham Shui Po</t>
+  </si>
+  <si>
+    <t>hr@nutrigeneai.com</t>
+  </si>
+  <si>
+    <t>Biotech / Lab</t>
+  </si>
+  <si>
+    <t>Graduate</t>
+  </si>
+  <si>
+    <t>Lab Routine</t>
+  </si>
+  <si>
+    <t>Admin, Procurement</t>
+  </si>
+  <si>
+    <t>Manage administrative paperwork &amp; reimbursements. Coordinate meetings with partners. Perform routine lab tasks (disinfection, sterilization). Conduct basic inventory checks for biotech research.</t>
+  </si>
+  <si>
+    <t>AI Biotech startup, Healthcare innovation, Cross-team coordination, Lab management.</t>
+  </si>
+  <si>
+    <t>EP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AEON Credit</t>
+  </si>
+  <si>
+    <t>Finance / MGMT</t>
+  </si>
+  <si>
+    <t>12 Months</t>
+  </si>
+  <si>
+    <t>Structured Thinking</t>
+  </si>
+  <si>
+    <t>AI Tools/Trends</t>
+  </si>
+  <si>
+    <t>12-month rotation program. Choose between Business Ops or Corporate Functions. Lead ESG &amp; digital projects. Gain exposure to listed financial ops &amp; AI integration. Fast-track to leadership.</t>
+  </si>
+  <si>
+    <t>Listed Company, Fortune 500 member, AI-focused MT stream, Mentorship &amp; Coaching.</t>
+  </si>
+  <si>
+    <t>EQ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://mapp.aeon.com.hk/jobapplication/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Postdoc Fellow</t>
+  </si>
+  <si>
+    <t>CNRM (CUHK)</t>
+  </si>
+  <si>
+    <t>R&amp;D / Biotech</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>Molecular Bio</t>
+  </si>
+  <si>
+    <t>3D Bioprinting, Animal Work</t>
+  </si>
+  <si>
+    <t>Conduct research on skeletal muscle diseases &amp; translational therapies. Perform cell culture, molecular biology, &amp; animal experiments. Assist PI in lab management.</t>
+  </si>
+  <si>
+    <t>Top-tier Research Center, HKSTP base, International consortium, Cutting-edge bioprinting tech.</t>
+  </si>
+  <si>
+    <t>ER</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI &amp; ERP GT</t>
+  </si>
+  <si>
+    <t>ERP / AI Biz</t>
+  </si>
+  <si>
+    <t>Numeric Sensitivity</t>
+  </si>
+  <si>
+    <t>Spark MLlib, TensorFlow</t>
+  </si>
+  <si>
+    <t>Rotate across Dev, Implementation &amp; R&amp;D. Provide AI-driven ERP consultation for enterprises. Conduct business analysis. Implement AI models into management systems. Travel to APAC &amp; Saudi Arabia.</t>
+  </si>
+  <si>
+    <t>High Starting Salary, Global travel (SEA/PRC/Saudi), Full SDLC exposure, In-house R&amp;D environment.</t>
+  </si>
+  <si>
+    <t>ES</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI &amp; Security Dev</t>
+  </si>
+  <si>
+    <t>eWalker</t>
+  </si>
+  <si>
+    <t>Kowloon City</t>
+  </si>
+  <si>
+    <t>recruit@ewalker.com.hk</t>
+  </si>
+  <si>
+    <t>CyberSec / Dev</t>
+  </si>
+  <si>
+    <t>Rust, Go, Python</t>
+  </si>
+  <si>
+    <t>AI/LLM, Big Data</t>
+  </si>
+  <si>
+    <t>Develop Big Data security &amp; forensics programs. Build AI/LLM applications for cybersecurity. Design systems in Windows environments. Integrate security into DevOps (DevSecOps). Full SDLC ownership.</t>
+  </si>
+  <si>
+    <t>High Starting Salary, Core R&amp;D role, Modern tech stack (Rust/Go), Impactful security tools.</t>
+  </si>
+  <si>
+    <t>ET</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CyberSec Trainee</t>
+  </si>
+  <si>
+    <t>Security / AI</t>
+  </si>
+  <si>
+    <t>Penetration Test</t>
+  </si>
+  <si>
+    <t>AI/LLM Testing, Web 3.0</t>
+  </si>
+  <si>
+    <t>Conduct AI/LLM security testing &amp; vulnerability assessments. Perform web/mobile penetration tests. Review Web 3.0 &amp; Smart Contract security. Document ISO 27001/ITIL compliance. Conduct cloud security &amp; forensic investigations.</t>
+  </si>
+  <si>
+    <t>Leading Security Firm, Red-team/Blue-team exposure, SOTA AI Security R&amp;D, Govt/MNC projects.</t>
+  </si>
+  <si>
+    <t>EU</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3069,9 +3832,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3091,6 +3854,14 @@
       <name val="新細明體"/>
       <family val="3"/>
       <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="新細明體"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -3126,19 +3897,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3438,7 +4212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N119"/>
+  <dimension ref="A1:N149"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
@@ -3446,4928 +4220,6161 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="N1" s="1"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>849</v>
+        <v>812</v>
       </c>
       <c r="B2" t="s">
-        <v>840</v>
+        <v>813</v>
       </c>
       <c r="C2" t="s">
-        <v>841</v>
+        <v>814</v>
       </c>
       <c r="D2" t="s">
-        <v>842</v>
-      </c>
-      <c r="E2" s="3">
-        <v>46189</v>
+        <v>208</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46136</v>
       </c>
       <c r="F2" t="s">
-        <v>843</v>
+        <v>815</v>
       </c>
       <c r="G2" t="s">
-        <v>844</v>
+        <v>816</v>
       </c>
       <c r="H2" t="s">
-        <v>422</v>
+        <v>817</v>
       </c>
       <c r="I2" t="s">
-        <v>845</v>
+        <v>666</v>
       </c>
       <c r="J2" t="s">
-        <v>846</v>
-      </c>
-      <c r="K2" t="s">
-        <v>847</v>
+        <v>818</v>
       </c>
       <c r="L2" t="s">
-        <v>848</v>
+        <v>819</v>
+      </c>
+      <c r="M2" t="s">
+        <v>820</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>742</v>
+        <v>1016</v>
       </c>
       <c r="B3" t="s">
-        <v>743</v>
+        <v>1006</v>
       </c>
       <c r="C3" t="s">
-        <v>724</v>
+        <v>1007</v>
       </c>
       <c r="D3" t="s">
-        <v>725</v>
-      </c>
-      <c r="E3" s="2">
-        <v>46139</v>
+        <v>1008</v>
+      </c>
+      <c r="E3" s="3">
+        <v>46226</v>
       </c>
       <c r="F3" t="s">
-        <v>726</v>
+        <v>1009</v>
       </c>
       <c r="G3" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="H3" t="s">
-        <v>518</v>
+        <v>1010</v>
       </c>
       <c r="I3" t="s">
-        <v>667</v>
+        <v>1011</v>
       </c>
       <c r="J3" t="s">
-        <v>744</v>
+        <v>1012</v>
       </c>
       <c r="K3" t="s">
-        <v>745</v>
+        <v>1013</v>
       </c>
       <c r="L3" t="s">
-        <v>746</v>
+        <v>1014</v>
       </c>
       <c r="M3" t="s">
-        <v>747</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>416</v>
+        <v>1023</v>
       </c>
       <c r="B4" t="s">
-        <v>417</v>
+        <v>1017</v>
       </c>
       <c r="C4" t="s">
-        <v>418</v>
+        <v>1007</v>
       </c>
       <c r="D4" t="s">
-        <v>220</v>
-      </c>
-      <c r="E4" s="2">
-        <v>46129</v>
+        <v>1008</v>
+      </c>
+      <c r="E4" s="3">
+        <v>46203</v>
       </c>
       <c r="F4" t="s">
-        <v>419</v>
+        <v>1009</v>
       </c>
       <c r="G4" t="s">
-        <v>420</v>
+        <v>666</v>
       </c>
       <c r="H4" t="s">
-        <v>421</v>
+        <v>1018</v>
       </c>
       <c r="I4" t="s">
-        <v>422</v>
+        <v>1011</v>
       </c>
       <c r="J4" t="s">
-        <v>194</v>
+        <v>1019</v>
       </c>
       <c r="K4" t="s">
-        <v>423</v>
+        <v>1020</v>
       </c>
       <c r="L4" t="s">
-        <v>424</v>
+        <v>1021</v>
       </c>
       <c r="M4" t="s">
-        <v>425</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>377</v>
+        <v>1030</v>
       </c>
       <c r="B5" t="s">
-        <v>378</v>
+        <v>1024</v>
       </c>
       <c r="C5" t="s">
-        <v>369</v>
+        <v>1007</v>
       </c>
       <c r="D5" t="s">
-        <v>220</v>
-      </c>
-      <c r="E5" s="2">
-        <v>46155</v>
+        <v>1008</v>
+      </c>
+      <c r="E5" s="3">
+        <v>46153</v>
       </c>
       <c r="F5" t="s">
-        <v>379</v>
+        <v>1009</v>
       </c>
       <c r="G5" t="s">
-        <v>380</v>
+        <v>666</v>
       </c>
       <c r="H5" t="s">
-        <v>223</v>
+        <v>1025</v>
       </c>
       <c r="I5" t="s">
-        <v>372</v>
+        <v>1011</v>
       </c>
       <c r="J5" t="s">
-        <v>194</v>
+        <v>1026</v>
       </c>
       <c r="K5" t="s">
-        <v>381</v>
+        <v>1027</v>
       </c>
       <c r="L5" t="s">
-        <v>382</v>
+        <v>1028</v>
       </c>
       <c r="M5" t="s">
-        <v>383</v>
-      </c>
-      <c r="N5" t="s">
-        <v>384</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>1005</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>996</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>997</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="2">
-        <v>46112</v>
+        <v>998</v>
+      </c>
+      <c r="E6" s="3">
+        <v>46220</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>999</v>
       </c>
       <c r="G6" t="s">
-        <v>65</v>
+        <v>666</v>
       </c>
       <c r="H6" t="s">
-        <v>58</v>
+        <v>1000</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>884</v>
       </c>
       <c r="J6" t="s">
-        <v>66</v>
+        <v>1001</v>
       </c>
       <c r="K6" t="s">
-        <v>67</v>
+        <v>1002</v>
       </c>
       <c r="L6" t="s">
-        <v>68</v>
+        <v>1003</v>
       </c>
       <c r="M6" t="s">
-        <v>69</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>568</v>
+        <v>838</v>
       </c>
       <c r="B7" t="s">
-        <v>569</v>
+        <v>829</v>
       </c>
       <c r="C7" t="s">
-        <v>570</v>
+        <v>830</v>
       </c>
       <c r="D7" t="s">
-        <v>571</v>
-      </c>
-      <c r="E7" s="2">
-        <v>46184</v>
+        <v>831</v>
+      </c>
+      <c r="E7" s="3">
+        <v>46142</v>
       </c>
       <c r="F7" t="s">
-        <v>572</v>
+        <v>832</v>
       </c>
       <c r="G7" t="s">
-        <v>573</v>
+        <v>833</v>
       </c>
       <c r="H7" t="s">
-        <v>574</v>
+        <v>57</v>
       </c>
       <c r="I7" t="s">
-        <v>519</v>
+        <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>575</v>
+        <v>834</v>
       </c>
       <c r="K7" t="s">
-        <v>576</v>
+        <v>835</v>
       </c>
       <c r="L7" t="s">
-        <v>577</v>
+        <v>836</v>
       </c>
       <c r="M7" t="s">
-        <v>578</v>
+        <v>837</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>839</v>
+        <v>550</v>
       </c>
       <c r="B8" t="s">
-        <v>830</v>
+        <v>551</v>
       </c>
       <c r="C8" t="s">
-        <v>831</v>
+        <v>552</v>
       </c>
       <c r="D8" t="s">
-        <v>832</v>
-      </c>
-      <c r="E8" s="3">
-        <v>46142</v>
+        <v>553</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46116</v>
       </c>
       <c r="F8" t="s">
-        <v>833</v>
+        <v>554</v>
       </c>
       <c r="G8" t="s">
-        <v>834</v>
+        <v>555</v>
       </c>
       <c r="H8" t="s">
-        <v>58</v>
+        <v>556</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
+        <v>557</v>
       </c>
       <c r="J8" t="s">
-        <v>835</v>
+        <v>558</v>
       </c>
       <c r="K8" t="s">
-        <v>836</v>
+        <v>559</v>
       </c>
       <c r="L8" t="s">
-        <v>837</v>
+        <v>560</v>
       </c>
       <c r="M8" t="s">
-        <v>838</v>
+        <v>561</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>282</v>
+        <v>562</v>
       </c>
       <c r="B9" t="s">
-        <v>283</v>
+        <v>563</v>
       </c>
       <c r="C9" t="s">
-        <v>284</v>
+        <v>552</v>
       </c>
       <c r="D9" t="s">
-        <v>285</v>
+        <v>553</v>
       </c>
       <c r="E9" s="2">
-        <v>46146</v>
+        <v>46116</v>
       </c>
       <c r="F9" t="s">
-        <v>286</v>
+        <v>554</v>
       </c>
       <c r="G9" t="s">
-        <v>287</v>
+        <v>555</v>
       </c>
       <c r="H9" t="s">
-        <v>288</v>
+        <v>556</v>
       </c>
       <c r="I9" t="s">
-        <v>289</v>
+        <v>557</v>
       </c>
       <c r="J9" t="s">
-        <v>194</v>
+        <v>558</v>
       </c>
       <c r="K9" t="s">
-        <v>290</v>
+        <v>564</v>
       </c>
       <c r="L9" t="s">
-        <v>291</v>
+        <v>565</v>
       </c>
       <c r="M9" t="s">
-        <v>292</v>
-      </c>
-      <c r="N9" t="s">
-        <v>293</v>
+        <v>566</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" s="2">
-        <v>46265</v>
+        <v>46136</v>
       </c>
       <c r="F10" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="G10" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="I10" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="J10" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="K10" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="L10" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="M10" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>860</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E11" s="2">
         <v>46136</v>
       </c>
       <c r="F11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G11" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J11" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="K11" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="L11" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M11" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>813</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s">
-        <v>814</v>
+        <v>123</v>
       </c>
       <c r="C12" t="s">
-        <v>815</v>
+        <v>124</v>
       </c>
       <c r="D12" t="s">
-        <v>209</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2">
         <v>46136</v>
       </c>
       <c r="F12" t="s">
-        <v>816</v>
+        <v>125</v>
       </c>
       <c r="G12" t="s">
-        <v>817</v>
+        <v>126</v>
       </c>
       <c r="H12" t="s">
-        <v>818</v>
+        <v>57</v>
       </c>
       <c r="I12" t="s">
-        <v>667</v>
+        <v>127</v>
       </c>
       <c r="J12" t="s">
-        <v>819</v>
+        <v>128</v>
+      </c>
+      <c r="K12" t="s">
+        <v>129</v>
       </c>
       <c r="L12" t="s">
-        <v>820</v>
+        <v>130</v>
       </c>
       <c r="M12" t="s">
-        <v>821</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B13" t="s">
-        <v>861</v>
+        <v>146</v>
       </c>
       <c r="C13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E13" s="2">
         <v>46136</v>
       </c>
       <c r="F13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G13" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J13" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="K13" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="L13" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M13" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>760</v>
+        <v>662</v>
       </c>
       <c r="B14" t="s">
-        <v>761</v>
+        <v>663</v>
       </c>
       <c r="C14" t="s">
-        <v>155</v>
+        <v>659</v>
       </c>
       <c r="D14" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E14" s="2">
-        <v>46135</v>
+        <v>46189</v>
       </c>
       <c r="F14" t="s">
-        <v>762</v>
+        <v>660</v>
       </c>
       <c r="G14" t="s">
-        <v>679</v>
+        <v>147</v>
       </c>
       <c r="H14" t="s">
+        <v>517</v>
+      </c>
+      <c r="I14" t="s">
         <v>518</v>
       </c>
-      <c r="I14" t="s">
-        <v>667</v>
-      </c>
       <c r="J14" t="s">
-        <v>763</v>
+        <v>628</v>
       </c>
       <c r="K14" t="s">
-        <v>764</v>
+        <v>629</v>
       </c>
       <c r="L14" t="s">
-        <v>765</v>
+        <v>630</v>
       </c>
       <c r="M14" t="s">
-        <v>766</v>
+        <v>664</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>595</v>
+        <v>677</v>
       </c>
       <c r="B15" t="s">
-        <v>596</v>
+        <v>652</v>
       </c>
       <c r="C15" t="s">
-        <v>590</v>
+        <v>659</v>
       </c>
       <c r="D15" t="s">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="E15" s="2">
         <v>46189</v>
       </c>
       <c r="F15" t="s">
-        <v>172</v>
+        <v>660</v>
       </c>
       <c r="G15" t="s">
-        <v>173</v>
+        <v>678</v>
       </c>
       <c r="H15" t="s">
-        <v>18</v>
+        <v>517</v>
       </c>
       <c r="I15" t="s">
-        <v>592</v>
+        <v>666</v>
       </c>
       <c r="J15" t="s">
-        <v>598</v>
+        <v>679</v>
       </c>
       <c r="K15" t="s">
-        <v>599</v>
+        <v>680</v>
       </c>
       <c r="L15" t="s">
-        <v>176</v>
+        <v>681</v>
       </c>
       <c r="M15" t="s">
-        <v>177</v>
+        <v>682</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>169</v>
+        <v>671</v>
       </c>
       <c r="B16" t="s">
-        <v>170</v>
+        <v>645</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>659</v>
       </c>
       <c r="D16" t="s">
-        <v>171</v>
+        <v>613</v>
       </c>
       <c r="E16" s="2">
-        <v>46265</v>
+        <v>46189</v>
       </c>
       <c r="F16" t="s">
-        <v>172</v>
+        <v>660</v>
       </c>
       <c r="G16" t="s">
-        <v>173</v>
+        <v>672</v>
       </c>
       <c r="H16" t="s">
-        <v>18</v>
+        <v>517</v>
       </c>
       <c r="I16" t="s">
-        <v>19</v>
+        <v>666</v>
       </c>
       <c r="J16" t="s">
-        <v>174</v>
+        <v>673</v>
       </c>
       <c r="K16" t="s">
-        <v>175</v>
+        <v>674</v>
       </c>
       <c r="L16" t="s">
-        <v>176</v>
+        <v>675</v>
       </c>
       <c r="M16" t="s">
-        <v>177</v>
+        <v>676</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>178</v>
+        <v>658</v>
       </c>
       <c r="B17" t="s">
-        <v>179</v>
+        <v>633</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>659</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>613</v>
       </c>
       <c r="E17" s="2">
-        <v>46265</v>
+        <v>46189</v>
       </c>
       <c r="F17" t="s">
-        <v>180</v>
+        <v>660</v>
       </c>
       <c r="G17" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="H17" t="s">
-        <v>18</v>
+        <v>517</v>
       </c>
       <c r="I17" t="s">
-        <v>19</v>
+        <v>518</v>
       </c>
       <c r="J17" t="s">
-        <v>182</v>
+        <v>661</v>
       </c>
       <c r="K17" t="s">
-        <v>183</v>
+        <v>629</v>
       </c>
       <c r="L17" t="s">
-        <v>184</v>
+        <v>635</v>
       </c>
       <c r="M17" t="s">
-        <v>185</v>
+        <v>636</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>589</v>
+        <v>665</v>
       </c>
       <c r="B18" t="s">
-        <v>179</v>
+        <v>638</v>
       </c>
       <c r="C18" t="s">
-        <v>590</v>
+        <v>659</v>
       </c>
       <c r="D18" t="s">
-        <v>591</v>
+        <v>613</v>
       </c>
       <c r="E18" s="2">
         <v>46189</v>
       </c>
       <c r="F18" t="s">
-        <v>180</v>
+        <v>660</v>
       </c>
       <c r="G18" t="s">
-        <v>181</v>
+        <v>639</v>
       </c>
       <c r="H18" t="s">
-        <v>18</v>
+        <v>517</v>
       </c>
       <c r="I18" t="s">
-        <v>592</v>
+        <v>666</v>
       </c>
       <c r="J18" t="s">
-        <v>593</v>
+        <v>667</v>
       </c>
       <c r="K18" t="s">
-        <v>594</v>
+        <v>668</v>
       </c>
       <c r="L18" t="s">
-        <v>184</v>
+        <v>669</v>
       </c>
       <c r="M18" t="s">
-        <v>185</v>
+        <v>670</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>627</v>
+        <v>512</v>
       </c>
       <c r="B19" t="s">
-        <v>628</v>
+        <v>513</v>
       </c>
       <c r="C19" t="s">
-        <v>613</v>
+        <v>505</v>
       </c>
       <c r="D19" t="s">
-        <v>614</v>
+        <v>514</v>
       </c>
       <c r="E19" s="2">
-        <v>46189</v>
+        <v>46183</v>
       </c>
       <c r="F19" t="s">
-        <v>615</v>
+        <v>515</v>
       </c>
       <c r="G19" t="s">
-        <v>148</v>
+        <v>516</v>
       </c>
       <c r="H19" t="s">
+        <v>517</v>
+      </c>
+      <c r="I19" t="s">
         <v>518</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>519</v>
       </c>
-      <c r="J19" t="s">
-        <v>629</v>
-      </c>
       <c r="K19" t="s">
-        <v>630</v>
+        <v>520</v>
       </c>
       <c r="L19" t="s">
-        <v>631</v>
+        <v>521</v>
       </c>
       <c r="M19" t="s">
-        <v>632</v>
+        <v>522</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>663</v>
+        <v>503</v>
       </c>
       <c r="B20" t="s">
-        <v>664</v>
+        <v>504</v>
       </c>
       <c r="C20" t="s">
-        <v>660</v>
+        <v>505</v>
       </c>
       <c r="D20" t="s">
-        <v>614</v>
+        <v>318</v>
       </c>
       <c r="E20" s="2">
-        <v>46189</v>
+        <v>46183</v>
       </c>
       <c r="F20" t="s">
-        <v>661</v>
+        <v>506</v>
       </c>
       <c r="G20" t="s">
-        <v>148</v>
+        <v>504</v>
       </c>
       <c r="H20" t="s">
-        <v>518</v>
+        <v>321</v>
       </c>
       <c r="I20" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="J20" t="s">
-        <v>629</v>
+        <v>193</v>
       </c>
       <c r="K20" t="s">
-        <v>630</v>
+        <v>508</v>
       </c>
       <c r="L20" t="s">
-        <v>631</v>
+        <v>509</v>
       </c>
       <c r="M20" t="s">
-        <v>665</v>
+        <v>510</v>
+      </c>
+      <c r="N20" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>652</v>
+        <v>700</v>
       </c>
       <c r="B21" t="s">
-        <v>653</v>
+        <v>701</v>
       </c>
       <c r="C21" t="s">
-        <v>613</v>
+        <v>702</v>
       </c>
       <c r="D21" t="s">
-        <v>614</v>
+        <v>703</v>
       </c>
       <c r="E21" s="2">
-        <v>46189</v>
+        <v>46147</v>
       </c>
       <c r="F21" t="s">
-        <v>615</v>
+        <v>704</v>
       </c>
       <c r="G21" t="s">
-        <v>654</v>
+        <v>678</v>
       </c>
       <c r="H21" t="s">
-        <v>518</v>
+        <v>705</v>
       </c>
       <c r="I21" t="s">
-        <v>519</v>
+        <v>666</v>
       </c>
       <c r="J21" t="s">
-        <v>655</v>
-      </c>
-      <c r="K21" t="s">
-        <v>656</v>
+        <v>706</v>
       </c>
       <c r="L21" t="s">
-        <v>657</v>
+        <v>707</v>
       </c>
       <c r="M21" t="s">
-        <v>658</v>
+        <v>708</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>709</v>
+      </c>
+      <c r="B22" t="s">
+        <v>710</v>
+      </c>
+      <c r="C22" t="s">
+        <v>702</v>
+      </c>
+      <c r="D22" t="s">
+        <v>703</v>
+      </c>
+      <c r="E22" s="2">
+        <v>46147</v>
+      </c>
+      <c r="F22" t="s">
+        <v>711</v>
+      </c>
+      <c r="G22" t="s">
         <v>678</v>
       </c>
-      <c r="B22" t="s">
-        <v>653</v>
-      </c>
-      <c r="C22" t="s">
-        <v>660</v>
-      </c>
-      <c r="D22" t="s">
-        <v>614</v>
-      </c>
-      <c r="E22" s="2">
-        <v>46189</v>
-      </c>
-      <c r="F22" t="s">
-        <v>661</v>
-      </c>
-      <c r="G22" t="s">
-        <v>679</v>
-      </c>
       <c r="H22" t="s">
-        <v>518</v>
+        <v>705</v>
       </c>
       <c r="I22" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J22" t="s">
-        <v>680</v>
-      </c>
-      <c r="K22" t="s">
-        <v>681</v>
-      </c>
-      <c r="L22" t="s">
-        <v>682</v>
+        <v>712</v>
       </c>
       <c r="M22" t="s">
-        <v>683</v>
+        <v>713</v>
+      </c>
+      <c r="N22" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>465</v>
+        <v>715</v>
       </c>
       <c r="B23" t="s">
-        <v>466</v>
+        <v>716</v>
       </c>
       <c r="C23" t="s">
-        <v>467</v>
+        <v>702</v>
       </c>
       <c r="D23" t="s">
-        <v>209</v>
+        <v>703</v>
       </c>
       <c r="E23" s="2">
-        <v>46173</v>
+        <v>46147</v>
       </c>
       <c r="F23" t="s">
-        <v>468</v>
+        <v>704</v>
       </c>
       <c r="G23" t="s">
-        <v>466</v>
+        <v>678</v>
       </c>
       <c r="H23" t="s">
-        <v>469</v>
+        <v>705</v>
       </c>
       <c r="I23" t="s">
-        <v>470</v>
+        <v>666</v>
       </c>
       <c r="J23" t="s">
-        <v>194</v>
+        <v>717</v>
       </c>
       <c r="K23" t="s">
-        <v>471</v>
+        <v>718</v>
       </c>
       <c r="L23" t="s">
-        <v>472</v>
+        <v>719</v>
       </c>
       <c r="M23" t="s">
-        <v>473</v>
-      </c>
-      <c r="N23" t="s">
-        <v>474</v>
+        <v>720</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>645</v>
+        <v>415</v>
       </c>
       <c r="B24" t="s">
-        <v>646</v>
+        <v>416</v>
       </c>
       <c r="C24" t="s">
-        <v>613</v>
+        <v>417</v>
       </c>
       <c r="D24" t="s">
-        <v>614</v>
+        <v>219</v>
       </c>
       <c r="E24" s="2">
-        <v>46189</v>
+        <v>46129</v>
       </c>
       <c r="F24" t="s">
-        <v>615</v>
+        <v>418</v>
       </c>
       <c r="G24" t="s">
-        <v>647</v>
+        <v>419</v>
       </c>
       <c r="H24" t="s">
-        <v>518</v>
+        <v>420</v>
       </c>
       <c r="I24" t="s">
-        <v>519</v>
+        <v>421</v>
       </c>
       <c r="J24" t="s">
-        <v>648</v>
+        <v>193</v>
       </c>
       <c r="K24" t="s">
-        <v>649</v>
+        <v>422</v>
       </c>
       <c r="L24" t="s">
-        <v>650</v>
+        <v>423</v>
       </c>
       <c r="M24" t="s">
-        <v>651</v>
+        <v>424</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>672</v>
+        <v>205</v>
       </c>
       <c r="B25" t="s">
-        <v>646</v>
+        <v>206</v>
       </c>
       <c r="C25" t="s">
-        <v>660</v>
+        <v>207</v>
       </c>
       <c r="D25" t="s">
-        <v>614</v>
+        <v>208</v>
       </c>
       <c r="E25" s="2">
-        <v>46189</v>
+        <v>46142</v>
       </c>
       <c r="F25" t="s">
-        <v>661</v>
+        <v>209</v>
       </c>
       <c r="G25" t="s">
-        <v>673</v>
+        <v>210</v>
       </c>
       <c r="H25" t="s">
-        <v>518</v>
+        <v>211</v>
       </c>
       <c r="I25" t="s">
-        <v>667</v>
+        <v>192</v>
       </c>
       <c r="J25" t="s">
-        <v>674</v>
+        <v>193</v>
       </c>
       <c r="K25" t="s">
-        <v>675</v>
+        <v>212</v>
       </c>
       <c r="L25" t="s">
-        <v>676</v>
+        <v>213</v>
       </c>
       <c r="M25" t="s">
-        <v>677</v>
+        <v>214</v>
+      </c>
+      <c r="N25" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>600</v>
+        <v>348</v>
       </c>
       <c r="B26" t="s">
-        <v>601</v>
+        <v>349</v>
       </c>
       <c r="C26" t="s">
-        <v>602</v>
+        <v>339</v>
       </c>
       <c r="D26" t="s">
-        <v>603</v>
+        <v>318</v>
       </c>
       <c r="E26" s="2">
-        <v>46187</v>
+        <v>46142</v>
       </c>
       <c r="F26" t="s">
-        <v>604</v>
+        <v>341</v>
       </c>
       <c r="G26" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="H26" t="s">
-        <v>605</v>
+        <v>343</v>
       </c>
       <c r="I26" t="s">
-        <v>606</v>
+        <v>344</v>
       </c>
       <c r="J26" t="s">
-        <v>607</v>
+        <v>193</v>
       </c>
       <c r="K26" t="s">
-        <v>608</v>
+        <v>351</v>
       </c>
       <c r="L26" t="s">
-        <v>609</v>
+        <v>352</v>
       </c>
       <c r="M26" t="s">
-        <v>610</v>
+        <v>353</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>483</v>
+        <v>337</v>
       </c>
       <c r="B27" t="s">
-        <v>484</v>
+        <v>338</v>
       </c>
       <c r="C27" t="s">
-        <v>485</v>
+        <v>339</v>
       </c>
       <c r="D27" t="s">
-        <v>486</v>
+        <v>340</v>
       </c>
       <c r="E27" s="2">
-        <v>46130</v>
+        <v>46142</v>
       </c>
       <c r="F27" t="s">
-        <v>487</v>
+        <v>341</v>
       </c>
       <c r="G27" t="s">
-        <v>488</v>
+        <v>342</v>
       </c>
       <c r="H27" t="s">
-        <v>489</v>
+        <v>343</v>
       </c>
       <c r="I27" t="s">
-        <v>128</v>
+        <v>344</v>
       </c>
       <c r="J27" t="s">
-        <v>490</v>
+        <v>193</v>
       </c>
       <c r="K27" t="s">
-        <v>491</v>
+        <v>345</v>
       </c>
       <c r="L27" t="s">
-        <v>492</v>
+        <v>346</v>
       </c>
       <c r="M27" t="s">
-        <v>493</v>
+        <v>347</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>425</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>426</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>427</v>
       </c>
       <c r="D28" t="s">
-        <v>15</v>
+        <v>219</v>
       </c>
       <c r="E28" s="2">
-        <v>46265</v>
+        <v>46116</v>
       </c>
       <c r="F28" t="s">
-        <v>33</v>
+        <v>428</v>
       </c>
       <c r="G28" t="s">
-        <v>34</v>
+        <v>429</v>
       </c>
       <c r="H28" t="s">
-        <v>18</v>
+        <v>430</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>431</v>
       </c>
       <c r="J28" t="s">
-        <v>35</v>
+        <v>193</v>
       </c>
       <c r="K28" t="s">
-        <v>36</v>
+        <v>432</v>
       </c>
       <c r="L28" t="s">
-        <v>37</v>
+        <v>433</v>
       </c>
       <c r="M28" t="s">
-        <v>38</v>
+        <v>434</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>1057</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>1047</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>1048</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" s="2">
-        <v>46265</v>
+        <v>1049</v>
+      </c>
+      <c r="E29" s="3">
+        <v>46226</v>
       </c>
       <c r="F29" t="s">
-        <v>16</v>
+        <v>1050</v>
       </c>
       <c r="G29" t="s">
-        <v>17</v>
+        <v>666</v>
       </c>
       <c r="H29" t="s">
-        <v>18</v>
+        <v>1051</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>1011</v>
       </c>
       <c r="J29" t="s">
-        <v>20</v>
+        <v>1052</v>
       </c>
       <c r="K29" t="s">
-        <v>21</v>
+        <v>1053</v>
       </c>
       <c r="L29" t="s">
-        <v>22</v>
+        <v>1054</v>
       </c>
       <c r="M29" t="s">
-        <v>23</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>315</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>316</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>317</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>318</v>
       </c>
       <c r="E30" s="2">
-        <v>46265</v>
+        <v>46151</v>
       </c>
       <c r="F30" t="s">
-        <v>41</v>
+        <v>319</v>
       </c>
       <c r="G30" t="s">
-        <v>42</v>
+        <v>320</v>
       </c>
       <c r="H30" t="s">
-        <v>18</v>
+        <v>321</v>
       </c>
       <c r="I30" t="s">
-        <v>19</v>
+        <v>299</v>
       </c>
       <c r="J30" t="s">
-        <v>43</v>
+        <v>322</v>
       </c>
       <c r="K30" t="s">
-        <v>44</v>
+        <v>323</v>
       </c>
       <c r="L30" t="s">
-        <v>45</v>
+        <v>324</v>
       </c>
       <c r="M30" t="s">
-        <v>23</v>
+        <v>325</v>
+      </c>
+      <c r="N30" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" t="s">
         <v>14</v>
-      </c>
-      <c r="D31" t="s">
-        <v>15</v>
       </c>
       <c r="E31" s="2">
         <v>46265</v>
       </c>
       <c r="F31" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="G31" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="H31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I31" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="J31" t="s">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="K31" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="L31" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="M31" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>494</v>
+        <v>967</v>
       </c>
       <c r="B32" t="s">
-        <v>495</v>
+        <v>959</v>
       </c>
       <c r="C32" t="s">
-        <v>496</v>
+        <v>960</v>
       </c>
       <c r="D32" t="s">
-        <v>497</v>
-      </c>
-      <c r="E32" s="2">
-        <v>46165</v>
+        <v>613</v>
+      </c>
+      <c r="E32" s="3">
+        <v>46173</v>
       </c>
       <c r="F32" t="s">
-        <v>498</v>
+        <v>961</v>
       </c>
       <c r="G32" t="s">
-        <v>495</v>
+        <v>666</v>
       </c>
       <c r="H32" t="s">
-        <v>499</v>
+        <v>962</v>
       </c>
       <c r="I32" t="s">
-        <v>500</v>
+        <v>884</v>
       </c>
       <c r="J32" t="s">
-        <v>194</v>
+        <v>963</v>
       </c>
       <c r="K32" t="s">
-        <v>501</v>
+        <v>964</v>
       </c>
       <c r="L32" t="s">
-        <v>502</v>
+        <v>965</v>
       </c>
       <c r="M32" t="s">
-        <v>503</v>
+        <v>966</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>123</v>
+        <v>948</v>
       </c>
       <c r="B33" t="s">
-        <v>124</v>
+        <v>940</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>941</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" s="2">
-        <v>46136</v>
+        <v>913</v>
+      </c>
+      <c r="E33" s="3">
+        <v>46212</v>
       </c>
       <c r="F33" t="s">
-        <v>126</v>
+        <v>942</v>
       </c>
       <c r="G33" t="s">
-        <v>127</v>
+        <v>666</v>
       </c>
       <c r="H33" t="s">
-        <v>58</v>
+        <v>943</v>
       </c>
       <c r="I33" t="s">
-        <v>128</v>
+        <v>884</v>
       </c>
       <c r="J33" t="s">
-        <v>129</v>
+        <v>944</v>
       </c>
       <c r="K33" t="s">
-        <v>130</v>
+        <v>945</v>
       </c>
       <c r="L33" t="s">
-        <v>131</v>
+        <v>946</v>
       </c>
       <c r="M33" t="s">
-        <v>132</v>
+        <v>947</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>217</v>
+        <v>985</v>
       </c>
       <c r="B34" t="s">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="C34" t="s">
-        <v>219</v>
+        <v>977</v>
       </c>
       <c r="D34" t="s">
-        <v>220</v>
-      </c>
-      <c r="E34" s="2">
-        <v>46132</v>
+        <v>978</v>
+      </c>
+      <c r="E34" s="3">
+        <v>46203</v>
       </c>
       <c r="F34" t="s">
-        <v>221</v>
+        <v>979</v>
       </c>
       <c r="G34" t="s">
-        <v>222</v>
+        <v>666</v>
       </c>
       <c r="H34" t="s">
-        <v>223</v>
+        <v>980</v>
       </c>
       <c r="I34" t="s">
-        <v>224</v>
+        <v>884</v>
       </c>
       <c r="J34" t="s">
-        <v>194</v>
+        <v>981</v>
       </c>
       <c r="K34" t="s">
-        <v>225</v>
+        <v>982</v>
       </c>
       <c r="L34" t="s">
-        <v>226</v>
+        <v>983</v>
       </c>
       <c r="M34" t="s">
-        <v>227</v>
-      </c>
-      <c r="N34" t="s">
-        <v>228</v>
+        <v>984</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>542</v>
+        <v>995</v>
       </c>
       <c r="B35" t="s">
-        <v>543</v>
+        <v>986</v>
       </c>
       <c r="C35" t="s">
-        <v>438</v>
+        <v>987</v>
       </c>
       <c r="D35" t="s">
-        <v>534</v>
-      </c>
-      <c r="E35" s="2">
-        <v>46184</v>
+        <v>724</v>
+      </c>
+      <c r="E35" s="3">
+        <v>46146</v>
       </c>
       <c r="F35" t="s">
-        <v>544</v>
+        <v>988</v>
       </c>
       <c r="G35" t="s">
-        <v>545</v>
+        <v>989</v>
       </c>
       <c r="H35" t="s">
-        <v>537</v>
+        <v>990</v>
       </c>
       <c r="I35" t="s">
-        <v>546</v>
+        <v>884</v>
       </c>
       <c r="J35" t="s">
-        <v>547</v>
+        <v>994</v>
       </c>
       <c r="K35" t="s">
-        <v>548</v>
+        <v>991</v>
       </c>
       <c r="L35" t="s">
-        <v>549</v>
+        <v>992</v>
       </c>
       <c r="M35" t="s">
-        <v>550</v>
+        <v>993</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>731</v>
+        <v>523</v>
       </c>
       <c r="B36" t="s">
-        <v>732</v>
+        <v>199</v>
       </c>
       <c r="C36" t="s">
-        <v>733</v>
+        <v>524</v>
       </c>
       <c r="D36" t="s">
-        <v>734</v>
+        <v>485</v>
       </c>
       <c r="E36" s="2">
-        <v>46117</v>
+        <v>46173</v>
       </c>
       <c r="F36" t="s">
-        <v>735</v>
+        <v>525</v>
       </c>
       <c r="G36" t="s">
-        <v>736</v>
+        <v>147</v>
       </c>
       <c r="H36" t="s">
-        <v>737</v>
+        <v>526</v>
       </c>
       <c r="I36" t="s">
-        <v>667</v>
+        <v>518</v>
       </c>
       <c r="J36" t="s">
-        <v>738</v>
+        <v>527</v>
+      </c>
+      <c r="K36" t="s">
+        <v>528</v>
       </c>
       <c r="L36" t="s">
-        <v>739</v>
+        <v>529</v>
       </c>
       <c r="M36" t="s">
-        <v>740</v>
-      </c>
-      <c r="N36" t="s">
-        <v>741</v>
+        <v>530</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>113</v>
+        <v>821</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>822</v>
       </c>
       <c r="C37" t="s">
-        <v>115</v>
+        <v>823</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
+        <v>219</v>
       </c>
       <c r="E37" s="2">
-        <v>46112</v>
+        <v>46125</v>
       </c>
       <c r="F37" t="s">
-        <v>116</v>
+        <v>824</v>
       </c>
       <c r="G37" t="s">
-        <v>117</v>
+        <v>825</v>
       </c>
       <c r="H37" t="s">
-        <v>118</v>
+        <v>420</v>
       </c>
       <c r="I37" t="s">
-        <v>19</v>
+        <v>666</v>
       </c>
       <c r="J37" t="s">
-        <v>119</v>
-      </c>
-      <c r="K37" t="s">
-        <v>120</v>
+        <v>826</v>
       </c>
       <c r="L37" t="s">
-        <v>121</v>
+        <v>827</v>
       </c>
       <c r="M37" t="s">
-        <v>122</v>
+        <v>828</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>822</v>
+        <v>112</v>
       </c>
       <c r="B38" t="s">
-        <v>823</v>
+        <v>113</v>
       </c>
       <c r="C38" t="s">
-        <v>824</v>
+        <v>114</v>
       </c>
       <c r="D38" t="s">
-        <v>220</v>
+        <v>14</v>
       </c>
       <c r="E38" s="2">
-        <v>46125</v>
+        <v>46112</v>
       </c>
       <c r="F38" t="s">
-        <v>825</v>
+        <v>115</v>
       </c>
       <c r="G38" t="s">
-        <v>826</v>
+        <v>116</v>
       </c>
       <c r="H38" t="s">
-        <v>421</v>
+        <v>117</v>
       </c>
       <c r="I38" t="s">
-        <v>667</v>
+        <v>18</v>
       </c>
       <c r="J38" t="s">
-        <v>827</v>
+        <v>118</v>
+      </c>
+      <c r="K38" t="s">
+        <v>119</v>
       </c>
       <c r="L38" t="s">
-        <v>828</v>
+        <v>120</v>
       </c>
       <c r="M38" t="s">
-        <v>829</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>633</v>
+        <v>976</v>
       </c>
       <c r="B39" t="s">
-        <v>634</v>
+        <v>968</v>
       </c>
       <c r="C39" t="s">
-        <v>613</v>
+        <v>969</v>
       </c>
       <c r="D39" t="s">
-        <v>614</v>
-      </c>
-      <c r="E39" s="2">
-        <v>46189</v>
+        <v>514</v>
+      </c>
+      <c r="E39" s="3">
+        <v>46173</v>
       </c>
       <c r="F39" t="s">
-        <v>615</v>
+        <v>970</v>
       </c>
       <c r="G39" t="s">
-        <v>148</v>
+        <v>666</v>
       </c>
       <c r="H39" t="s">
-        <v>518</v>
+        <v>971</v>
       </c>
       <c r="I39" t="s">
-        <v>519</v>
+        <v>884</v>
       </c>
       <c r="J39" t="s">
-        <v>635</v>
+        <v>972</v>
       </c>
       <c r="K39" t="s">
-        <v>630</v>
+        <v>973</v>
       </c>
       <c r="L39" t="s">
-        <v>636</v>
+        <v>974</v>
       </c>
       <c r="M39" t="s">
-        <v>637</v>
+        <v>975</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>659</v>
+        <v>859</v>
       </c>
       <c r="B40" t="s">
-        <v>634</v>
+        <v>850</v>
       </c>
       <c r="C40" t="s">
-        <v>660</v>
+        <v>851</v>
       </c>
       <c r="D40" t="s">
-        <v>614</v>
-      </c>
-      <c r="E40" s="2">
-        <v>46189</v>
+        <v>14</v>
+      </c>
+      <c r="E40" s="3">
+        <v>46133</v>
       </c>
       <c r="F40" t="s">
-        <v>661</v>
+        <v>852</v>
       </c>
       <c r="G40" t="s">
-        <v>148</v>
+        <v>853</v>
       </c>
       <c r="H40" t="s">
-        <v>518</v>
+        <v>854</v>
       </c>
       <c r="I40" t="s">
-        <v>519</v>
+        <v>18</v>
       </c>
       <c r="J40" t="s">
-        <v>662</v>
+        <v>855</v>
       </c>
       <c r="K40" t="s">
-        <v>630</v>
+        <v>856</v>
       </c>
       <c r="L40" t="s">
-        <v>636</v>
+        <v>857</v>
       </c>
       <c r="M40" t="s">
-        <v>637</v>
+        <v>858</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>475</v>
+        <v>398</v>
       </c>
       <c r="B41" t="s">
-        <v>476</v>
+        <v>399</v>
       </c>
       <c r="C41" t="s">
-        <v>467</v>
+        <v>386</v>
       </c>
       <c r="D41" t="s">
-        <v>209</v>
+        <v>318</v>
       </c>
       <c r="E41" s="2">
-        <v>46173</v>
+        <v>46155</v>
       </c>
       <c r="F41" t="s">
-        <v>477</v>
+        <v>387</v>
       </c>
       <c r="G41" t="s">
-        <v>476</v>
+        <v>399</v>
       </c>
       <c r="H41" t="s">
-        <v>478</v>
+        <v>389</v>
       </c>
       <c r="I41" t="s">
-        <v>479</v>
+        <v>390</v>
       </c>
       <c r="J41" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K41" t="s">
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="L41" t="s">
-        <v>481</v>
+        <v>401</v>
       </c>
       <c r="M41" t="s">
-        <v>482</v>
+        <v>402</v>
+      </c>
+      <c r="N41" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>186</v>
+        <v>404</v>
       </c>
       <c r="B42" t="s">
-        <v>187</v>
+        <v>405</v>
       </c>
       <c r="C42" t="s">
-        <v>188</v>
+        <v>386</v>
       </c>
       <c r="D42" t="s">
-        <v>189</v>
+        <v>318</v>
       </c>
       <c r="E42" s="2">
-        <v>46113</v>
+        <v>46155</v>
       </c>
       <c r="F42" t="s">
-        <v>190</v>
+        <v>387</v>
       </c>
       <c r="G42" t="s">
-        <v>191</v>
+        <v>405</v>
       </c>
       <c r="H42" t="s">
-        <v>192</v>
+        <v>389</v>
       </c>
       <c r="I42" t="s">
+        <v>390</v>
+      </c>
+      <c r="J42" t="s">
         <v>193</v>
       </c>
-      <c r="J42" t="s">
-        <v>194</v>
-      </c>
       <c r="K42" t="s">
-        <v>195</v>
+        <v>406</v>
       </c>
       <c r="L42" t="s">
-        <v>196</v>
+        <v>407</v>
       </c>
       <c r="M42" t="s">
-        <v>197</v>
-      </c>
-      <c r="N42" t="s">
-        <v>198</v>
+        <v>408</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>436</v>
+        <v>409</v>
       </c>
       <c r="B43" t="s">
-        <v>437</v>
+        <v>410</v>
       </c>
       <c r="C43" t="s">
-        <v>438</v>
+        <v>386</v>
       </c>
       <c r="D43" t="s">
-        <v>285</v>
+        <v>318</v>
       </c>
       <c r="E43" s="2">
-        <v>46176</v>
+        <v>46155</v>
       </c>
       <c r="F43" t="s">
-        <v>439</v>
+        <v>387</v>
       </c>
       <c r="G43" t="s">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="H43" t="s">
-        <v>431</v>
+        <v>389</v>
       </c>
       <c r="I43" t="s">
-        <v>441</v>
+        <v>390</v>
       </c>
       <c r="J43" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K43" t="s">
-        <v>442</v>
+        <v>411</v>
       </c>
       <c r="L43" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="M43" t="s">
-        <v>444</v>
+        <v>413</v>
       </c>
       <c r="N43" t="s">
-        <v>445</v>
+        <v>414</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>199</v>
+        <v>384</v>
       </c>
       <c r="B44" t="s">
-        <v>200</v>
+        <v>385</v>
       </c>
       <c r="C44" t="s">
-        <v>188</v>
+        <v>386</v>
       </c>
       <c r="D44" t="s">
-        <v>189</v>
+        <v>318</v>
       </c>
       <c r="E44" s="2">
-        <v>46113</v>
+        <v>46155</v>
       </c>
       <c r="F44" t="s">
-        <v>190</v>
+        <v>387</v>
       </c>
       <c r="G44" t="s">
-        <v>201</v>
+        <v>388</v>
       </c>
       <c r="H44" t="s">
-        <v>192</v>
+        <v>389</v>
       </c>
       <c r="I44" t="s">
+        <v>390</v>
+      </c>
+      <c r="J44" t="s">
         <v>193</v>
       </c>
-      <c r="J44" t="s">
-        <v>194</v>
-      </c>
       <c r="K44" t="s">
-        <v>202</v>
+        <v>391</v>
       </c>
       <c r="L44" t="s">
-        <v>203</v>
+        <v>392</v>
       </c>
       <c r="M44" t="s">
-        <v>204</v>
+        <v>393</v>
       </c>
       <c r="N44" t="s">
-        <v>205</v>
+        <v>394</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>524</v>
+        <v>395</v>
       </c>
       <c r="B45" t="s">
-        <v>200</v>
+        <v>396</v>
       </c>
       <c r="C45" t="s">
-        <v>525</v>
+        <v>386</v>
       </c>
       <c r="D45" t="s">
-        <v>486</v>
+        <v>318</v>
       </c>
       <c r="E45" s="2">
-        <v>46173</v>
+        <v>46155</v>
       </c>
       <c r="F45" t="s">
-        <v>526</v>
+        <v>387</v>
       </c>
       <c r="G45" t="s">
-        <v>148</v>
+        <v>396</v>
       </c>
       <c r="H45" t="s">
-        <v>527</v>
+        <v>389</v>
       </c>
       <c r="I45" t="s">
-        <v>519</v>
+        <v>390</v>
       </c>
       <c r="J45" t="s">
-        <v>528</v>
+        <v>193</v>
       </c>
       <c r="K45" t="s">
-        <v>529</v>
+        <v>391</v>
       </c>
       <c r="L45" t="s">
-        <v>530</v>
+        <v>392</v>
       </c>
       <c r="M45" t="s">
-        <v>531</v>
+        <v>393</v>
+      </c>
+      <c r="N45" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>446</v>
+        <v>239</v>
       </c>
       <c r="B46" t="s">
-        <v>447</v>
+        <v>240</v>
       </c>
       <c r="C46" t="s">
-        <v>438</v>
+        <v>230</v>
       </c>
       <c r="D46" t="s">
-        <v>285</v>
+        <v>219</v>
       </c>
       <c r="E46" s="2">
-        <v>46176</v>
+        <v>46139</v>
       </c>
       <c r="F46" t="s">
-        <v>448</v>
+        <v>241</v>
       </c>
       <c r="G46" t="s">
-        <v>449</v>
+        <v>242</v>
       </c>
       <c r="H46" t="s">
-        <v>431</v>
+        <v>233</v>
       </c>
       <c r="I46" t="s">
-        <v>441</v>
+        <v>234</v>
       </c>
       <c r="J46" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K46" t="s">
-        <v>450</v>
+        <v>243</v>
       </c>
       <c r="L46" t="s">
-        <v>451</v>
+        <v>244</v>
       </c>
       <c r="M46" t="s">
-        <v>452</v>
+        <v>245</v>
       </c>
       <c r="N46" t="s">
-        <v>453</v>
+        <v>246</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>807</v>
+        <v>253</v>
       </c>
       <c r="B47" t="s">
-        <v>808</v>
+        <v>254</v>
       </c>
       <c r="C47" t="s">
-        <v>724</v>
+        <v>230</v>
       </c>
       <c r="D47" t="s">
-        <v>273</v>
+        <v>219</v>
       </c>
       <c r="E47" s="2">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="F47" t="s">
-        <v>726</v>
+        <v>255</v>
       </c>
       <c r="G47" t="s">
-        <v>679</v>
+        <v>256</v>
       </c>
       <c r="H47" t="s">
-        <v>809</v>
+        <v>233</v>
       </c>
       <c r="I47" t="s">
-        <v>667</v>
+        <v>234</v>
       </c>
       <c r="J47" t="s">
-        <v>810</v>
+        <v>193</v>
+      </c>
+      <c r="K47" t="s">
+        <v>257</v>
       </c>
       <c r="L47" t="s">
-        <v>811</v>
+        <v>258</v>
       </c>
       <c r="M47" t="s">
-        <v>812</v>
+        <v>259</v>
+      </c>
+      <c r="N47" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>551</v>
+        <v>261</v>
       </c>
       <c r="B48" t="s">
-        <v>552</v>
+        <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>553</v>
+        <v>230</v>
       </c>
       <c r="D48" t="s">
-        <v>554</v>
+        <v>219</v>
       </c>
       <c r="E48" s="2">
-        <v>46116</v>
+        <v>46139</v>
       </c>
       <c r="F48" t="s">
-        <v>555</v>
+        <v>263</v>
       </c>
       <c r="G48" t="s">
-        <v>556</v>
+        <v>264</v>
       </c>
       <c r="H48" t="s">
-        <v>557</v>
+        <v>233</v>
       </c>
       <c r="I48" t="s">
-        <v>558</v>
+        <v>234</v>
       </c>
       <c r="J48" t="s">
-        <v>559</v>
+        <v>193</v>
       </c>
       <c r="K48" t="s">
-        <v>560</v>
+        <v>265</v>
       </c>
       <c r="L48" t="s">
-        <v>561</v>
+        <v>266</v>
       </c>
       <c r="M48" t="s">
-        <v>562</v>
+        <v>267</v>
+      </c>
+      <c r="N48" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>563</v>
+        <v>247</v>
       </c>
       <c r="B49" t="s">
-        <v>564</v>
+        <v>146</v>
       </c>
       <c r="C49" t="s">
-        <v>553</v>
+        <v>230</v>
       </c>
       <c r="D49" t="s">
-        <v>554</v>
+        <v>219</v>
       </c>
       <c r="E49" s="2">
-        <v>46116</v>
+        <v>46139</v>
       </c>
       <c r="F49" t="s">
-        <v>555</v>
+        <v>248</v>
       </c>
       <c r="G49" t="s">
-        <v>556</v>
+        <v>147</v>
       </c>
       <c r="H49" t="s">
-        <v>557</v>
+        <v>233</v>
       </c>
       <c r="I49" t="s">
-        <v>558</v>
+        <v>234</v>
       </c>
       <c r="J49" t="s">
-        <v>559</v>
+        <v>193</v>
       </c>
       <c r="K49" t="s">
-        <v>565</v>
+        <v>249</v>
       </c>
       <c r="L49" t="s">
-        <v>566</v>
+        <v>250</v>
       </c>
       <c r="M49" t="s">
-        <v>567</v>
+        <v>251</v>
+      </c>
+      <c r="N49" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>767</v>
+        <v>228</v>
       </c>
       <c r="B50" t="s">
-        <v>768</v>
+        <v>229</v>
       </c>
       <c r="C50" t="s">
-        <v>769</v>
+        <v>230</v>
       </c>
       <c r="D50" t="s">
-        <v>486</v>
+        <v>219</v>
       </c>
       <c r="E50" s="2">
-        <v>46158</v>
+        <v>46139</v>
       </c>
       <c r="F50" t="s">
-        <v>770</v>
+        <v>231</v>
       </c>
       <c r="G50" t="s">
-        <v>736</v>
+        <v>232</v>
       </c>
       <c r="H50" t="s">
-        <v>706</v>
+        <v>233</v>
       </c>
       <c r="I50" t="s">
-        <v>667</v>
+        <v>234</v>
       </c>
       <c r="J50" t="s">
-        <v>771</v>
+        <v>193</v>
+      </c>
+      <c r="K50" t="s">
+        <v>235</v>
+      </c>
+      <c r="L50" t="s">
+        <v>236</v>
       </c>
       <c r="M50" t="s">
-        <v>772</v>
+        <v>237</v>
       </c>
       <c r="N50" t="s">
-        <v>773</v>
+        <v>238</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>774</v>
+        <v>730</v>
       </c>
       <c r="B51" t="s">
-        <v>775</v>
+        <v>731</v>
       </c>
       <c r="C51" t="s">
-        <v>769</v>
+        <v>732</v>
       </c>
       <c r="D51" t="s">
-        <v>486</v>
+        <v>733</v>
       </c>
       <c r="E51" s="2">
-        <v>46158</v>
+        <v>46117</v>
       </c>
       <c r="F51" t="s">
-        <v>770</v>
+        <v>734</v>
       </c>
       <c r="G51" t="s">
+        <v>735</v>
+      </c>
+      <c r="H51" t="s">
         <v>736</v>
       </c>
-      <c r="H51" t="s">
-        <v>706</v>
-      </c>
       <c r="I51" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J51" t="s">
-        <v>771</v>
+        <v>737</v>
+      </c>
+      <c r="L51" t="s">
+        <v>738</v>
       </c>
       <c r="M51" t="s">
-        <v>776</v>
+        <v>739</v>
       </c>
       <c r="N51" t="s">
-        <v>777</v>
+        <v>740</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>778</v>
+        <v>877</v>
       </c>
       <c r="B52" t="s">
-        <v>779</v>
+        <v>868</v>
       </c>
       <c r="C52" t="s">
-        <v>769</v>
+        <v>869</v>
       </c>
       <c r="D52" t="s">
-        <v>486</v>
-      </c>
-      <c r="E52" s="2">
-        <v>46158</v>
+        <v>870</v>
+      </c>
+      <c r="E52" s="3">
+        <v>46387</v>
       </c>
       <c r="F52" t="s">
-        <v>770</v>
+        <v>871</v>
       </c>
       <c r="G52" t="s">
-        <v>736</v>
+        <v>853</v>
       </c>
       <c r="H52" t="s">
-        <v>706</v>
+        <v>872</v>
       </c>
       <c r="I52" t="s">
-        <v>667</v>
+        <v>18</v>
       </c>
       <c r="J52" t="s">
-        <v>780</v>
+        <v>873</v>
+      </c>
+      <c r="K52" t="s">
+        <v>874</v>
+      </c>
+      <c r="L52" t="s">
+        <v>875</v>
       </c>
       <c r="M52" t="s">
-        <v>781</v>
-      </c>
-      <c r="N52" t="s">
-        <v>777</v>
+        <v>876</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>305</v>
+        <v>376</v>
       </c>
       <c r="B53" t="s">
-        <v>306</v>
+        <v>377</v>
       </c>
       <c r="C53" t="s">
-        <v>307</v>
+        <v>368</v>
       </c>
       <c r="D53" t="s">
-        <v>308</v>
+        <v>219</v>
       </c>
       <c r="E53" s="2">
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="F53" t="s">
-        <v>309</v>
+        <v>378</v>
       </c>
       <c r="G53" t="s">
-        <v>310</v>
+        <v>379</v>
       </c>
       <c r="H53" t="s">
-        <v>311</v>
+        <v>222</v>
       </c>
       <c r="I53" t="s">
-        <v>312</v>
+        <v>371</v>
       </c>
       <c r="J53" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K53" t="s">
-        <v>313</v>
+        <v>380</v>
       </c>
       <c r="L53" t="s">
-        <v>314</v>
+        <v>381</v>
       </c>
       <c r="M53" t="s">
-        <v>315</v>
+        <v>382</v>
+      </c>
+      <c r="N53" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>426</v>
+        <v>366</v>
       </c>
       <c r="B54" t="s">
-        <v>427</v>
+        <v>367</v>
       </c>
       <c r="C54" t="s">
-        <v>428</v>
+        <v>368</v>
       </c>
       <c r="D54" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E54" s="2">
-        <v>46116</v>
+        <v>46155</v>
       </c>
       <c r="F54" t="s">
-        <v>429</v>
+        <v>369</v>
       </c>
       <c r="G54" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="H54" t="s">
-        <v>431</v>
+        <v>222</v>
       </c>
       <c r="I54" t="s">
-        <v>432</v>
+        <v>371</v>
       </c>
       <c r="J54" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K54" t="s">
-        <v>433</v>
+        <v>372</v>
       </c>
       <c r="L54" t="s">
-        <v>434</v>
+        <v>373</v>
       </c>
       <c r="M54" t="s">
-        <v>435</v>
+        <v>374</v>
+      </c>
+      <c r="N54" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>454</v>
+        <v>920</v>
       </c>
       <c r="B55" t="s">
-        <v>455</v>
+        <v>911</v>
       </c>
       <c r="C55" t="s">
-        <v>456</v>
+        <v>912</v>
       </c>
       <c r="D55" t="s">
-        <v>457</v>
-      </c>
-      <c r="E55" s="2">
-        <v>46176</v>
+        <v>913</v>
+      </c>
+      <c r="E55" s="3">
+        <v>46162</v>
       </c>
       <c r="F55" t="s">
-        <v>458</v>
+        <v>914</v>
       </c>
       <c r="G55" t="s">
-        <v>459</v>
+        <v>666</v>
       </c>
       <c r="H55" t="s">
-        <v>460</v>
+        <v>915</v>
       </c>
       <c r="I55" t="s">
-        <v>461</v>
+        <v>884</v>
       </c>
       <c r="J55" t="s">
-        <v>194</v>
+        <v>916</v>
       </c>
       <c r="K55" t="s">
-        <v>462</v>
+        <v>917</v>
       </c>
       <c r="L55" t="s">
-        <v>463</v>
+        <v>918</v>
       </c>
       <c r="M55" t="s">
-        <v>464</v>
+        <v>919</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>692</v>
+        <v>788</v>
       </c>
       <c r="B56" t="s">
-        <v>693</v>
+        <v>789</v>
       </c>
       <c r="C56" t="s">
-        <v>694</v>
+        <v>790</v>
       </c>
       <c r="D56" t="s">
-        <v>486</v>
+        <v>307</v>
       </c>
       <c r="E56" s="2">
-        <v>46118</v>
+        <v>46198</v>
       </c>
       <c r="F56" t="s">
-        <v>695</v>
+        <v>791</v>
       </c>
       <c r="G56" t="s">
-        <v>679</v>
+        <v>792</v>
       </c>
       <c r="H56" t="s">
-        <v>696</v>
+        <v>793</v>
       </c>
       <c r="I56" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J56" t="s">
-        <v>697</v>
-      </c>
-      <c r="K56" t="s">
-        <v>698</v>
+        <v>794</v>
       </c>
       <c r="L56" t="s">
-        <v>699</v>
+        <v>795</v>
       </c>
       <c r="M56" t="s">
-        <v>700</v>
+        <v>796</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>513</v>
+        <v>741</v>
       </c>
       <c r="B57" t="s">
-        <v>514</v>
+        <v>742</v>
       </c>
       <c r="C57" t="s">
-        <v>506</v>
+        <v>723</v>
       </c>
       <c r="D57" t="s">
-        <v>515</v>
+        <v>724</v>
       </c>
       <c r="E57" s="2">
-        <v>46183</v>
+        <v>46139</v>
       </c>
       <c r="F57" t="s">
-        <v>516</v>
+        <v>725</v>
       </c>
       <c r="G57" t="s">
+        <v>678</v>
+      </c>
+      <c r="H57" t="s">
         <v>517</v>
       </c>
-      <c r="H57" t="s">
-        <v>518</v>
-      </c>
       <c r="I57" t="s">
-        <v>519</v>
+        <v>666</v>
       </c>
       <c r="J57" t="s">
-        <v>520</v>
+        <v>743</v>
       </c>
       <c r="K57" t="s">
-        <v>521</v>
+        <v>744</v>
       </c>
       <c r="L57" t="s">
-        <v>522</v>
+        <v>745</v>
       </c>
       <c r="M57" t="s">
-        <v>523</v>
+        <v>746</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>701</v>
+        <v>806</v>
       </c>
       <c r="B58" t="s">
-        <v>702</v>
+        <v>807</v>
       </c>
       <c r="C58" t="s">
-        <v>703</v>
+        <v>723</v>
       </c>
       <c r="D58" t="s">
-        <v>704</v>
+        <v>272</v>
       </c>
       <c r="E58" s="2">
-        <v>46147</v>
+        <v>46142</v>
       </c>
       <c r="F58" t="s">
-        <v>705</v>
+        <v>725</v>
       </c>
       <c r="G58" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H58" t="s">
-        <v>706</v>
+        <v>808</v>
       </c>
       <c r="I58" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J58" t="s">
-        <v>707</v>
+        <v>809</v>
       </c>
       <c r="L58" t="s">
-        <v>708</v>
+        <v>810</v>
       </c>
       <c r="M58" t="s">
-        <v>709</v>
+        <v>811</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>532</v>
+        <v>721</v>
       </c>
       <c r="B59" t="s">
-        <v>533</v>
+        <v>722</v>
       </c>
       <c r="C59" t="s">
-        <v>438</v>
+        <v>723</v>
       </c>
       <c r="D59" t="s">
-        <v>534</v>
+        <v>724</v>
       </c>
       <c r="E59" s="2">
-        <v>46184</v>
+        <v>46125</v>
       </c>
       <c r="F59" t="s">
-        <v>535</v>
+        <v>725</v>
       </c>
       <c r="G59" t="s">
-        <v>536</v>
+        <v>678</v>
       </c>
       <c r="H59" t="s">
-        <v>537</v>
+        <v>517</v>
       </c>
       <c r="I59" t="s">
-        <v>519</v>
+        <v>666</v>
       </c>
       <c r="J59" t="s">
-        <v>538</v>
+        <v>726</v>
       </c>
       <c r="K59" t="s">
-        <v>539</v>
+        <v>727</v>
       </c>
       <c r="L59" t="s">
-        <v>540</v>
+        <v>728</v>
       </c>
       <c r="M59" t="s">
-        <v>541</v>
+        <v>729</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>153</v>
+        <v>683</v>
       </c>
       <c r="B60" t="s">
-        <v>154</v>
+        <v>684</v>
       </c>
       <c r="C60" t="s">
-        <v>155</v>
+        <v>685</v>
       </c>
       <c r="D60" t="s">
-        <v>15</v>
+        <v>307</v>
       </c>
       <c r="E60" s="2">
-        <v>46128</v>
+        <v>46143</v>
       </c>
       <c r="F60" t="s">
-        <v>156</v>
+        <v>686</v>
       </c>
       <c r="G60" t="s">
-        <v>148</v>
+        <v>556</v>
       </c>
       <c r="H60" t="s">
-        <v>58</v>
+        <v>556</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
+        <v>666</v>
       </c>
       <c r="J60" t="s">
-        <v>157</v>
+        <v>687</v>
       </c>
       <c r="K60" t="s">
-        <v>158</v>
+        <v>688</v>
       </c>
       <c r="L60" t="s">
-        <v>159</v>
+        <v>689</v>
       </c>
       <c r="M60" t="s">
-        <v>160</v>
+        <v>690</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>710</v>
+        <v>304</v>
       </c>
       <c r="B61" t="s">
-        <v>711</v>
+        <v>305</v>
       </c>
       <c r="C61" t="s">
-        <v>703</v>
+        <v>306</v>
       </c>
       <c r="D61" t="s">
-        <v>704</v>
+        <v>307</v>
       </c>
       <c r="E61" s="2">
         <v>46147</v>
       </c>
       <c r="F61" t="s">
-        <v>712</v>
+        <v>308</v>
       </c>
       <c r="G61" t="s">
-        <v>679</v>
+        <v>309</v>
       </c>
       <c r="H61" t="s">
-        <v>706</v>
+        <v>310</v>
       </c>
       <c r="I61" t="s">
-        <v>667</v>
+        <v>311</v>
       </c>
       <c r="J61" t="s">
-        <v>713</v>
+        <v>193</v>
+      </c>
+      <c r="K61" t="s">
+        <v>312</v>
+      </c>
+      <c r="L61" t="s">
+        <v>313</v>
       </c>
       <c r="M61" t="s">
-        <v>714</v>
-      </c>
-      <c r="N61" t="s">
-        <v>715</v>
+        <v>314</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>716</v>
+        <v>910</v>
       </c>
       <c r="B62" t="s">
-        <v>717</v>
+        <v>900</v>
       </c>
       <c r="C62" t="s">
-        <v>703</v>
+        <v>901</v>
       </c>
       <c r="D62" t="s">
-        <v>704</v>
-      </c>
-      <c r="E62" s="2">
-        <v>46147</v>
+        <v>902</v>
+      </c>
+      <c r="E62" s="3">
+        <v>46142</v>
       </c>
       <c r="F62" t="s">
-        <v>705</v>
+        <v>903</v>
       </c>
       <c r="G62" t="s">
-        <v>679</v>
+        <v>904</v>
       </c>
       <c r="H62" t="s">
-        <v>706</v>
+        <v>825</v>
       </c>
       <c r="I62" t="s">
-        <v>667</v>
+        <v>905</v>
       </c>
       <c r="J62" t="s">
-        <v>718</v>
+        <v>906</v>
       </c>
       <c r="K62" t="s">
-        <v>719</v>
+        <v>907</v>
       </c>
       <c r="L62" t="s">
-        <v>720</v>
+        <v>908</v>
       </c>
       <c r="M62" t="s">
-        <v>721</v>
+        <v>909</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>754</v>
+        <v>453</v>
       </c>
       <c r="B63" t="s">
-        <v>755</v>
+        <v>454</v>
       </c>
       <c r="C63" t="s">
-        <v>155</v>
+        <v>455</v>
       </c>
       <c r="D63" t="s">
-        <v>614</v>
+        <v>456</v>
       </c>
       <c r="E63" s="2">
-        <v>46135</v>
+        <v>46176</v>
       </c>
       <c r="F63" t="s">
-        <v>156</v>
+        <v>457</v>
       </c>
       <c r="G63" t="s">
-        <v>679</v>
+        <v>458</v>
       </c>
       <c r="H63" t="s">
-        <v>518</v>
+        <v>459</v>
       </c>
       <c r="I63" t="s">
-        <v>667</v>
+        <v>460</v>
       </c>
       <c r="J63" t="s">
-        <v>756</v>
+        <v>193</v>
       </c>
       <c r="K63" t="s">
-        <v>757</v>
+        <v>461</v>
       </c>
       <c r="L63" t="s">
-        <v>758</v>
+        <v>462</v>
       </c>
       <c r="M63" t="s">
-        <v>759</v>
+        <v>463</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>240</v>
+        <v>759</v>
       </c>
       <c r="B64" t="s">
-        <v>241</v>
+        <v>760</v>
       </c>
       <c r="C64" t="s">
-        <v>231</v>
+        <v>154</v>
       </c>
       <c r="D64" t="s">
-        <v>220</v>
+        <v>613</v>
       </c>
       <c r="E64" s="2">
-        <v>46139</v>
+        <v>46135</v>
       </c>
       <c r="F64" t="s">
-        <v>242</v>
+        <v>761</v>
       </c>
       <c r="G64" t="s">
-        <v>243</v>
+        <v>678</v>
       </c>
       <c r="H64" t="s">
-        <v>234</v>
+        <v>517</v>
       </c>
       <c r="I64" t="s">
-        <v>235</v>
+        <v>666</v>
       </c>
       <c r="J64" t="s">
-        <v>194</v>
+        <v>762</v>
       </c>
       <c r="K64" t="s">
-        <v>244</v>
+        <v>763</v>
       </c>
       <c r="L64" t="s">
-        <v>245</v>
+        <v>764</v>
       </c>
       <c r="M64" t="s">
-        <v>246</v>
-      </c>
-      <c r="N64" t="s">
-        <v>247</v>
+        <v>765</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>399</v>
+        <v>867</v>
       </c>
       <c r="B65" t="s">
-        <v>400</v>
+        <v>861</v>
       </c>
       <c r="C65" t="s">
-        <v>387</v>
+        <v>154</v>
       </c>
       <c r="D65" t="s">
-        <v>319</v>
-      </c>
-      <c r="E65" s="2">
-        <v>46155</v>
+        <v>14</v>
+      </c>
+      <c r="E65" s="3">
+        <v>46159</v>
       </c>
       <c r="F65" t="s">
-        <v>388</v>
+        <v>761</v>
       </c>
       <c r="G65" t="s">
-        <v>400</v>
+        <v>853</v>
       </c>
       <c r="H65" t="s">
-        <v>390</v>
+        <v>862</v>
       </c>
       <c r="I65" t="s">
-        <v>391</v>
+        <v>18</v>
       </c>
       <c r="J65" t="s">
-        <v>194</v>
+        <v>863</v>
       </c>
       <c r="K65" t="s">
-        <v>401</v>
+        <v>864</v>
       </c>
       <c r="L65" t="s">
-        <v>402</v>
+        <v>865</v>
       </c>
       <c r="M65" t="s">
-        <v>403</v>
-      </c>
-      <c r="N65" t="s">
-        <v>404</v>
+        <v>866</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>53</v>
+        <v>152</v>
       </c>
       <c r="B66" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="C66" t="s">
-        <v>55</v>
+        <v>154</v>
       </c>
       <c r="D66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E66" s="2">
-        <v>46112</v>
+        <v>46128</v>
       </c>
       <c r="F66" t="s">
-        <v>56</v>
+        <v>155</v>
       </c>
       <c r="G66" t="s">
+        <v>147</v>
+      </c>
+      <c r="H66" t="s">
         <v>57</v>
       </c>
-      <c r="H66" t="s">
-        <v>58</v>
-      </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J66" t="s">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="K66" t="s">
-        <v>60</v>
+        <v>157</v>
       </c>
       <c r="L66" t="s">
-        <v>61</v>
+        <v>158</v>
       </c>
       <c r="M66" t="s">
-        <v>62</v>
+        <v>159</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>328</v>
+        <v>753</v>
       </c>
       <c r="B67" t="s">
-        <v>329</v>
+        <v>754</v>
       </c>
       <c r="C67" t="s">
-        <v>330</v>
+        <v>154</v>
       </c>
       <c r="D67" t="s">
-        <v>285</v>
+        <v>613</v>
       </c>
       <c r="E67" s="2">
-        <v>46142</v>
+        <v>46135</v>
       </c>
       <c r="F67" t="s">
-        <v>331</v>
+        <v>155</v>
       </c>
       <c r="G67" t="s">
-        <v>329</v>
+        <v>678</v>
       </c>
       <c r="H67" t="s">
-        <v>332</v>
+        <v>517</v>
       </c>
       <c r="I67" t="s">
-        <v>333</v>
+        <v>666</v>
       </c>
       <c r="J67" t="s">
-        <v>194</v>
+        <v>755</v>
       </c>
       <c r="K67" t="s">
-        <v>334</v>
+        <v>756</v>
       </c>
       <c r="L67" t="s">
-        <v>335</v>
+        <v>757</v>
       </c>
       <c r="M67" t="s">
-        <v>336</v>
-      </c>
-      <c r="N67" t="s">
-        <v>337</v>
+        <v>758</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>789</v>
+        <v>160</v>
       </c>
       <c r="B68" t="s">
-        <v>790</v>
+        <v>161</v>
       </c>
       <c r="C68" t="s">
-        <v>791</v>
+        <v>154</v>
       </c>
       <c r="D68" t="s">
-        <v>308</v>
+        <v>14</v>
       </c>
       <c r="E68" s="2">
-        <v>46198</v>
+        <v>46128</v>
       </c>
       <c r="F68" t="s">
-        <v>792</v>
+        <v>162</v>
       </c>
       <c r="G68" t="s">
-        <v>793</v>
+        <v>163</v>
       </c>
       <c r="H68" t="s">
-        <v>794</v>
+        <v>57</v>
       </c>
       <c r="I68" t="s">
-        <v>667</v>
+        <v>18</v>
       </c>
       <c r="J68" t="s">
-        <v>795</v>
+        <v>164</v>
+      </c>
+      <c r="K68" t="s">
+        <v>165</v>
       </c>
       <c r="L68" t="s">
-        <v>796</v>
+        <v>166</v>
       </c>
       <c r="M68" t="s">
-        <v>797</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>349</v>
+        <v>747</v>
       </c>
       <c r="B69" t="s">
-        <v>350</v>
+        <v>748</v>
       </c>
       <c r="C69" t="s">
-        <v>340</v>
+        <v>154</v>
       </c>
       <c r="D69" t="s">
-        <v>319</v>
+        <v>613</v>
       </c>
       <c r="E69" s="2">
-        <v>46142</v>
+        <v>46135</v>
       </c>
       <c r="F69" t="s">
-        <v>342</v>
+        <v>162</v>
       </c>
       <c r="G69" t="s">
-        <v>351</v>
+        <v>672</v>
       </c>
       <c r="H69" t="s">
-        <v>344</v>
+        <v>517</v>
       </c>
       <c r="I69" t="s">
-        <v>345</v>
+        <v>666</v>
       </c>
       <c r="J69" t="s">
-        <v>194</v>
+        <v>749</v>
       </c>
       <c r="K69" t="s">
-        <v>352</v>
+        <v>750</v>
       </c>
       <c r="L69" t="s">
-        <v>353</v>
+        <v>751</v>
       </c>
       <c r="M69" t="s">
-        <v>354</v>
+        <v>752</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>338</v>
+        <v>930</v>
       </c>
       <c r="B70" t="s">
-        <v>339</v>
+        <v>921</v>
       </c>
       <c r="C70" t="s">
-        <v>340</v>
+        <v>922</v>
       </c>
       <c r="D70" t="s">
-        <v>341</v>
-      </c>
-      <c r="E70" s="2">
-        <v>46142</v>
+        <v>923</v>
+      </c>
+      <c r="E70" s="3">
+        <v>46173</v>
       </c>
       <c r="F70" t="s">
-        <v>342</v>
+        <v>924</v>
       </c>
       <c r="G70" t="s">
-        <v>343</v>
+        <v>666</v>
       </c>
       <c r="H70" t="s">
-        <v>344</v>
+        <v>925</v>
       </c>
       <c r="I70" t="s">
-        <v>345</v>
+        <v>884</v>
       </c>
       <c r="J70" t="s">
-        <v>194</v>
+        <v>926</v>
       </c>
       <c r="K70" t="s">
-        <v>346</v>
+        <v>927</v>
       </c>
       <c r="L70" t="s">
-        <v>347</v>
+        <v>928</v>
       </c>
       <c r="M70" t="s">
-        <v>348</v>
+        <v>929</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>722</v>
+        <v>185</v>
       </c>
       <c r="B71" t="s">
-        <v>723</v>
+        <v>186</v>
       </c>
       <c r="C71" t="s">
-        <v>724</v>
+        <v>187</v>
       </c>
       <c r="D71" t="s">
-        <v>725</v>
+        <v>188</v>
       </c>
       <c r="E71" s="2">
-        <v>46125</v>
+        <v>46113</v>
       </c>
       <c r="F71" t="s">
-        <v>726</v>
+        <v>189</v>
       </c>
       <c r="G71" t="s">
-        <v>679</v>
+        <v>190</v>
       </c>
       <c r="H71" t="s">
-        <v>518</v>
+        <v>191</v>
       </c>
       <c r="I71" t="s">
-        <v>667</v>
+        <v>192</v>
       </c>
       <c r="J71" t="s">
-        <v>727</v>
+        <v>193</v>
       </c>
       <c r="K71" t="s">
-        <v>728</v>
+        <v>194</v>
       </c>
       <c r="L71" t="s">
-        <v>729</v>
+        <v>195</v>
       </c>
       <c r="M71" t="s">
-        <v>730</v>
+        <v>196</v>
+      </c>
+      <c r="N71" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>782</v>
+        <v>198</v>
       </c>
       <c r="B72" t="s">
-        <v>783</v>
+        <v>199</v>
       </c>
       <c r="C72" t="s">
-        <v>769</v>
+        <v>187</v>
       </c>
       <c r="D72" t="s">
-        <v>486</v>
+        <v>188</v>
       </c>
       <c r="E72" s="2">
-        <v>46158</v>
+        <v>46113</v>
       </c>
       <c r="F72" t="s">
-        <v>770</v>
+        <v>189</v>
       </c>
       <c r="G72" t="s">
-        <v>784</v>
+        <v>200</v>
       </c>
       <c r="H72" t="s">
-        <v>785</v>
+        <v>191</v>
       </c>
       <c r="I72" t="s">
-        <v>667</v>
+        <v>192</v>
       </c>
       <c r="J72" t="s">
-        <v>786</v>
+        <v>193</v>
+      </c>
+      <c r="K72" t="s">
+        <v>201</v>
       </c>
       <c r="L72" t="s">
-        <v>787</v>
+        <v>202</v>
       </c>
       <c r="M72" t="s">
-        <v>788</v>
+        <v>203</v>
+      </c>
+      <c r="N72" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>504</v>
+        <v>216</v>
       </c>
       <c r="B73" t="s">
-        <v>505</v>
+        <v>217</v>
       </c>
       <c r="C73" t="s">
-        <v>506</v>
+        <v>218</v>
       </c>
       <c r="D73" t="s">
-        <v>319</v>
+        <v>219</v>
       </c>
       <c r="E73" s="2">
-        <v>46183</v>
+        <v>46132</v>
       </c>
       <c r="F73" t="s">
-        <v>507</v>
+        <v>220</v>
       </c>
       <c r="G73" t="s">
-        <v>505</v>
+        <v>221</v>
       </c>
       <c r="H73" t="s">
-        <v>322</v>
+        <v>222</v>
       </c>
       <c r="I73" t="s">
-        <v>508</v>
+        <v>223</v>
       </c>
       <c r="J73" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K73" t="s">
-        <v>509</v>
+        <v>224</v>
       </c>
       <c r="L73" t="s">
-        <v>510</v>
+        <v>225</v>
       </c>
       <c r="M73" t="s">
-        <v>511</v>
+        <v>226</v>
       </c>
       <c r="N73" t="s">
-        <v>512</v>
+        <v>227</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>405</v>
+        <v>594</v>
       </c>
       <c r="B74" t="s">
-        <v>406</v>
+        <v>595</v>
       </c>
       <c r="C74" t="s">
-        <v>387</v>
+        <v>589</v>
       </c>
       <c r="D74" t="s">
-        <v>319</v>
+        <v>596</v>
       </c>
       <c r="E74" s="2">
-        <v>46155</v>
+        <v>46189</v>
       </c>
       <c r="F74" t="s">
-        <v>388</v>
+        <v>171</v>
       </c>
       <c r="G74" t="s">
-        <v>406</v>
+        <v>172</v>
       </c>
       <c r="H74" t="s">
-        <v>390</v>
+        <v>17</v>
       </c>
       <c r="I74" t="s">
-        <v>391</v>
+        <v>591</v>
       </c>
       <c r="J74" t="s">
-        <v>194</v>
+        <v>597</v>
       </c>
       <c r="K74" t="s">
-        <v>407</v>
+        <v>598</v>
       </c>
       <c r="L74" t="s">
-        <v>408</v>
+        <v>175</v>
       </c>
       <c r="M74" t="s">
-        <v>409</v>
+        <v>176</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>254</v>
+        <v>588</v>
       </c>
       <c r="B75" t="s">
-        <v>255</v>
+        <v>178</v>
       </c>
       <c r="C75" t="s">
-        <v>231</v>
+        <v>589</v>
       </c>
       <c r="D75" t="s">
-        <v>220</v>
+        <v>590</v>
       </c>
       <c r="E75" s="2">
-        <v>46139</v>
+        <v>46189</v>
       </c>
       <c r="F75" t="s">
-        <v>256</v>
+        <v>179</v>
       </c>
       <c r="G75" t="s">
-        <v>257</v>
+        <v>180</v>
       </c>
       <c r="H75" t="s">
-        <v>234</v>
+        <v>17</v>
       </c>
       <c r="I75" t="s">
-        <v>235</v>
+        <v>591</v>
       </c>
       <c r="J75" t="s">
-        <v>194</v>
+        <v>592</v>
       </c>
       <c r="K75" t="s">
-        <v>258</v>
+        <v>593</v>
       </c>
       <c r="L75" t="s">
-        <v>259</v>
+        <v>183</v>
       </c>
       <c r="M75" t="s">
-        <v>260</v>
-      </c>
-      <c r="N75" t="s">
-        <v>261</v>
+        <v>184</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>262</v>
+        <v>168</v>
       </c>
       <c r="B76" t="s">
-        <v>263</v>
+        <v>169</v>
       </c>
       <c r="C76" t="s">
-        <v>231</v>
+        <v>13</v>
       </c>
       <c r="D76" t="s">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="E76" s="2">
-        <v>46139</v>
+        <v>46265</v>
       </c>
       <c r="F76" t="s">
-        <v>264</v>
+        <v>171</v>
       </c>
       <c r="G76" t="s">
-        <v>265</v>
+        <v>172</v>
       </c>
       <c r="H76" t="s">
-        <v>234</v>
+        <v>17</v>
       </c>
       <c r="I76" t="s">
-        <v>235</v>
+        <v>18</v>
       </c>
       <c r="J76" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="K76" t="s">
-        <v>266</v>
+        <v>174</v>
       </c>
       <c r="L76" t="s">
-        <v>267</v>
+        <v>175</v>
       </c>
       <c r="M76" t="s">
-        <v>268</v>
-      </c>
-      <c r="N76" t="s">
-        <v>269</v>
+        <v>176</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>355</v>
+        <v>177</v>
       </c>
       <c r="B77" t="s">
-        <v>356</v>
+        <v>178</v>
       </c>
       <c r="C77" t="s">
-        <v>357</v>
+        <v>13</v>
       </c>
       <c r="D77" t="s">
-        <v>209</v>
+        <v>14</v>
       </c>
       <c r="E77" s="2">
-        <v>46150</v>
+        <v>46265</v>
       </c>
       <c r="F77" t="s">
-        <v>358</v>
+        <v>179</v>
       </c>
       <c r="G77" t="s">
-        <v>359</v>
+        <v>180</v>
       </c>
       <c r="H77" t="s">
-        <v>360</v>
+        <v>17</v>
       </c>
       <c r="I77" t="s">
-        <v>361</v>
+        <v>18</v>
       </c>
       <c r="J77" t="s">
-        <v>362</v>
+        <v>181</v>
       </c>
       <c r="K77" t="s">
-        <v>363</v>
+        <v>182</v>
       </c>
       <c r="L77" t="s">
-        <v>364</v>
+        <v>183</v>
       </c>
       <c r="M77" t="s">
-        <v>365</v>
-      </c>
-      <c r="N77" t="s">
-        <v>366</v>
+        <v>184</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="B78" t="s">
-        <v>271</v>
+        <v>31</v>
       </c>
       <c r="C78" t="s">
-        <v>272</v>
+        <v>13</v>
       </c>
       <c r="D78" t="s">
-        <v>273</v>
+        <v>14</v>
       </c>
       <c r="E78" s="2">
-        <v>46142</v>
+        <v>46265</v>
       </c>
       <c r="F78" t="s">
-        <v>274</v>
+        <v>32</v>
       </c>
       <c r="G78" t="s">
-        <v>275</v>
+        <v>33</v>
       </c>
       <c r="H78" t="s">
-        <v>276</v>
+        <v>17</v>
       </c>
       <c r="I78" t="s">
-        <v>277</v>
+        <v>18</v>
       </c>
       <c r="J78" t="s">
-        <v>194</v>
+        <v>34</v>
       </c>
       <c r="K78" t="s">
-        <v>278</v>
+        <v>35</v>
       </c>
       <c r="L78" t="s">
-        <v>279</v>
+        <v>36</v>
       </c>
       <c r="M78" t="s">
-        <v>280</v>
-      </c>
-      <c r="N78" t="s">
-        <v>281</v>
+        <v>37</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>410</v>
+        <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>411</v>
+        <v>12</v>
       </c>
       <c r="C79" t="s">
-        <v>387</v>
+        <v>13</v>
       </c>
       <c r="D79" t="s">
-        <v>319</v>
+        <v>14</v>
       </c>
       <c r="E79" s="2">
-        <v>46155</v>
+        <v>46265</v>
       </c>
       <c r="F79" t="s">
-        <v>388</v>
+        <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>411</v>
+        <v>16</v>
       </c>
       <c r="H79" t="s">
-        <v>390</v>
+        <v>17</v>
       </c>
       <c r="I79" t="s">
-        <v>391</v>
+        <v>18</v>
       </c>
       <c r="J79" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
       <c r="K79" t="s">
-        <v>412</v>
+        <v>20</v>
       </c>
       <c r="L79" t="s">
-        <v>413</v>
+        <v>21</v>
       </c>
       <c r="M79" t="s">
-        <v>414</v>
-      </c>
-      <c r="N79" t="s">
-        <v>415</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>385</v>
+        <v>38</v>
       </c>
       <c r="B80" t="s">
-        <v>386</v>
+        <v>39</v>
       </c>
       <c r="C80" t="s">
-        <v>387</v>
+        <v>13</v>
       </c>
       <c r="D80" t="s">
-        <v>319</v>
+        <v>14</v>
       </c>
       <c r="E80" s="2">
-        <v>46155</v>
+        <v>46265</v>
       </c>
       <c r="F80" t="s">
-        <v>388</v>
+        <v>40</v>
       </c>
       <c r="G80" t="s">
-        <v>389</v>
+        <v>41</v>
       </c>
       <c r="H80" t="s">
-        <v>390</v>
+        <v>17</v>
       </c>
       <c r="I80" t="s">
-        <v>391</v>
+        <v>18</v>
       </c>
       <c r="J80" t="s">
-        <v>194</v>
+        <v>42</v>
       </c>
       <c r="K80" t="s">
-        <v>392</v>
+        <v>43</v>
       </c>
       <c r="L80" t="s">
-        <v>393</v>
+        <v>44</v>
       </c>
       <c r="M80" t="s">
-        <v>394</v>
-      </c>
-      <c r="N80" t="s">
-        <v>395</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="B81" t="s">
-        <v>147</v>
+        <v>24</v>
       </c>
       <c r="C81" t="s">
-        <v>125</v>
+        <v>13</v>
       </c>
       <c r="D81" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E81" s="2">
-        <v>46136</v>
+        <v>46265</v>
       </c>
       <c r="F81" t="s">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="G81" t="s">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="H81" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="I81" t="s">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="J81" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="K81" t="s">
-        <v>150</v>
+        <v>28</v>
       </c>
       <c r="L81" t="s">
-        <v>151</v>
+        <v>29</v>
       </c>
       <c r="M81" t="s">
-        <v>152</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="B82" t="s">
-        <v>147</v>
+        <v>878</v>
       </c>
       <c r="C82" t="s">
-        <v>231</v>
+        <v>13</v>
       </c>
       <c r="D82" t="s">
-        <v>220</v>
+        <v>14</v>
       </c>
       <c r="E82" s="2">
-        <v>46139</v>
+        <v>46265</v>
       </c>
       <c r="F82" t="s">
-        <v>249</v>
+        <v>46</v>
       </c>
       <c r="G82" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="H82" t="s">
-        <v>234</v>
+        <v>17</v>
       </c>
       <c r="I82" t="s">
-        <v>235</v>
+        <v>18</v>
       </c>
       <c r="J82" t="s">
-        <v>194</v>
+        <v>48</v>
       </c>
       <c r="K82" t="s">
-        <v>250</v>
+        <v>49</v>
       </c>
       <c r="L82" t="s">
-        <v>251</v>
+        <v>50</v>
       </c>
       <c r="M82" t="s">
-        <v>252</v>
-      </c>
-      <c r="N82" t="s">
-        <v>253</v>
+        <v>51</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>293</v>
+      </c>
+      <c r="B83" t="s">
+        <v>146</v>
+      </c>
+      <c r="C83" t="s">
         <v>294</v>
       </c>
-      <c r="B83" t="s">
-        <v>147</v>
-      </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
         <v>295</v>
-      </c>
-      <c r="D83" t="s">
-        <v>296</v>
       </c>
       <c r="E83" s="2">
         <v>46147</v>
       </c>
       <c r="F83" t="s">
+        <v>296</v>
+      </c>
+      <c r="G83" t="s">
         <v>297</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
         <v>298</v>
       </c>
-      <c r="H83" t="s">
+      <c r="I83" t="s">
         <v>299</v>
       </c>
-      <c r="I83" t="s">
+      <c r="J83" t="s">
+        <v>193</v>
+      </c>
+      <c r="K83" t="s">
         <v>300</v>
       </c>
-      <c r="J83" t="s">
-        <v>194</v>
-      </c>
-      <c r="K83" t="s">
+      <c r="L83" t="s">
         <v>301</v>
       </c>
-      <c r="L83" t="s">
+      <c r="M83" t="s">
         <v>302</v>
       </c>
-      <c r="M83" t="s">
+      <c r="N83" t="s">
         <v>303</v>
-      </c>
-      <c r="N83" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>611</v>
+        <v>958</v>
       </c>
       <c r="B84" t="s">
-        <v>612</v>
+        <v>949</v>
       </c>
       <c r="C84" t="s">
-        <v>613</v>
+        <v>950</v>
       </c>
       <c r="D84" t="s">
-        <v>614</v>
-      </c>
-      <c r="E84" s="2">
-        <v>46189</v>
+        <v>951</v>
+      </c>
+      <c r="E84" s="3">
+        <v>46152</v>
       </c>
       <c r="F84" t="s">
-        <v>615</v>
+        <v>952</v>
       </c>
       <c r="G84" t="s">
-        <v>148</v>
+        <v>666</v>
       </c>
       <c r="H84" t="s">
-        <v>518</v>
+        <v>953</v>
       </c>
       <c r="I84" t="s">
-        <v>519</v>
+        <v>884</v>
       </c>
       <c r="J84" t="s">
-        <v>616</v>
+        <v>954</v>
       </c>
       <c r="K84" t="s">
-        <v>617</v>
+        <v>955</v>
       </c>
       <c r="L84" t="s">
-        <v>618</v>
+        <v>956</v>
       </c>
       <c r="M84" t="s">
-        <v>619</v>
+        <v>957</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>161</v>
+        <v>354</v>
       </c>
       <c r="B85" t="s">
-        <v>162</v>
+        <v>355</v>
       </c>
       <c r="C85" t="s">
-        <v>155</v>
+        <v>356</v>
       </c>
       <c r="D85" t="s">
-        <v>15</v>
+        <v>208</v>
       </c>
       <c r="E85" s="2">
-        <v>46128</v>
+        <v>46150</v>
       </c>
       <c r="F85" t="s">
-        <v>163</v>
+        <v>357</v>
       </c>
       <c r="G85" t="s">
-        <v>164</v>
+        <v>358</v>
       </c>
       <c r="H85" t="s">
-        <v>58</v>
+        <v>359</v>
       </c>
       <c r="I85" t="s">
-        <v>19</v>
+        <v>360</v>
       </c>
       <c r="J85" t="s">
-        <v>165</v>
+        <v>361</v>
       </c>
       <c r="K85" t="s">
-        <v>166</v>
+        <v>362</v>
       </c>
       <c r="L85" t="s">
-        <v>167</v>
+        <v>363</v>
       </c>
       <c r="M85" t="s">
-        <v>168</v>
+        <v>364</v>
+      </c>
+      <c r="N85" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>748</v>
+        <v>482</v>
       </c>
       <c r="B86" t="s">
-        <v>749</v>
+        <v>483</v>
       </c>
       <c r="C86" t="s">
-        <v>155</v>
+        <v>484</v>
       </c>
       <c r="D86" t="s">
-        <v>614</v>
+        <v>485</v>
       </c>
       <c r="E86" s="2">
-        <v>46135</v>
+        <v>46130</v>
       </c>
       <c r="F86" t="s">
-        <v>163</v>
+        <v>486</v>
       </c>
       <c r="G86" t="s">
-        <v>673</v>
+        <v>487</v>
       </c>
       <c r="H86" t="s">
-        <v>518</v>
+        <v>488</v>
       </c>
       <c r="I86" t="s">
-        <v>667</v>
+        <v>127</v>
       </c>
       <c r="J86" t="s">
-        <v>750</v>
+        <v>489</v>
       </c>
       <c r="K86" t="s">
-        <v>751</v>
+        <v>490</v>
       </c>
       <c r="L86" t="s">
-        <v>752</v>
+        <v>491</v>
       </c>
       <c r="M86" t="s">
-        <v>753</v>
+        <v>492</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>206</v>
+        <v>899</v>
       </c>
       <c r="B87" t="s">
-        <v>207</v>
+        <v>890</v>
       </c>
       <c r="C87" t="s">
-        <v>208</v>
+        <v>891</v>
       </c>
       <c r="D87" t="s">
-        <v>209</v>
-      </c>
-      <c r="E87" s="2">
-        <v>46142</v>
+        <v>892</v>
+      </c>
+      <c r="E87" s="3">
+        <v>46204</v>
       </c>
       <c r="F87" t="s">
-        <v>210</v>
+        <v>893</v>
       </c>
       <c r="G87" t="s">
-        <v>211</v>
+        <v>853</v>
       </c>
       <c r="H87" t="s">
-        <v>212</v>
+        <v>894</v>
       </c>
       <c r="I87" t="s">
-        <v>193</v>
+        <v>18</v>
       </c>
       <c r="J87" t="s">
-        <v>194</v>
+        <v>895</v>
       </c>
       <c r="K87" t="s">
-        <v>213</v>
+        <v>896</v>
       </c>
       <c r="L87" t="s">
-        <v>214</v>
+        <v>897</v>
       </c>
       <c r="M87" t="s">
-        <v>215</v>
-      </c>
-      <c r="N87" t="s">
-        <v>216</v>
+        <v>898</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>620</v>
+        <v>889</v>
       </c>
       <c r="B88" t="s">
-        <v>621</v>
+        <v>879</v>
       </c>
       <c r="C88" t="s">
-        <v>613</v>
+        <v>880</v>
       </c>
       <c r="D88" t="s">
-        <v>614</v>
-      </c>
-      <c r="E88" s="2">
-        <v>46189</v>
+        <v>881</v>
+      </c>
+      <c r="E88" s="3">
+        <v>46204</v>
       </c>
       <c r="F88" t="s">
-        <v>615</v>
+        <v>882</v>
       </c>
       <c r="G88" t="s">
-        <v>622</v>
+        <v>853</v>
       </c>
       <c r="H88" t="s">
-        <v>518</v>
+        <v>883</v>
       </c>
       <c r="I88" t="s">
-        <v>519</v>
+        <v>884</v>
       </c>
       <c r="J88" t="s">
-        <v>623</v>
+        <v>885</v>
       </c>
       <c r="K88" t="s">
-        <v>624</v>
+        <v>886</v>
       </c>
       <c r="L88" t="s">
-        <v>625</v>
+        <v>887</v>
       </c>
       <c r="M88" t="s">
-        <v>626</v>
+        <v>888</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>46</v>
+        <v>327</v>
       </c>
       <c r="B89" t="s">
-        <v>879</v>
+        <v>328</v>
       </c>
       <c r="C89" t="s">
-        <v>14</v>
+        <v>329</v>
       </c>
       <c r="D89" t="s">
-        <v>15</v>
+        <v>284</v>
       </c>
       <c r="E89" s="2">
-        <v>46265</v>
+        <v>46142</v>
       </c>
       <c r="F89" t="s">
-        <v>47</v>
+        <v>330</v>
       </c>
       <c r="G89" t="s">
-        <v>48</v>
+        <v>328</v>
       </c>
       <c r="H89" t="s">
-        <v>18</v>
+        <v>331</v>
       </c>
       <c r="I89" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="J89" t="s">
-        <v>49</v>
+        <v>193</v>
       </c>
       <c r="K89" t="s">
-        <v>50</v>
+        <v>333</v>
       </c>
       <c r="L89" t="s">
-        <v>51</v>
+        <v>334</v>
       </c>
       <c r="M89" t="s">
-        <v>52</v>
+        <v>335</v>
+      </c>
+      <c r="N89" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>684</v>
+        <v>797</v>
       </c>
       <c r="B90" t="s">
-        <v>685</v>
+        <v>798</v>
       </c>
       <c r="C90" t="s">
-        <v>686</v>
+        <v>799</v>
       </c>
       <c r="D90" t="s">
-        <v>308</v>
+        <v>800</v>
       </c>
       <c r="E90" s="2">
-        <v>46143</v>
+        <v>46126</v>
       </c>
       <c r="F90" t="s">
-        <v>687</v>
+        <v>801</v>
       </c>
       <c r="G90" t="s">
-        <v>557</v>
+        <v>802</v>
       </c>
       <c r="H90" t="s">
-        <v>557</v>
+        <v>420</v>
       </c>
       <c r="I90" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J90" t="s">
-        <v>688</v>
-      </c>
-      <c r="K90" t="s">
-        <v>689</v>
+        <v>803</v>
       </c>
       <c r="L90" t="s">
-        <v>690</v>
+        <v>804</v>
       </c>
       <c r="M90" t="s">
-        <v>691</v>
+        <v>805</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>367</v>
+        <v>766</v>
       </c>
       <c r="B91" t="s">
-        <v>368</v>
+        <v>767</v>
       </c>
       <c r="C91" t="s">
-        <v>369</v>
+        <v>768</v>
       </c>
       <c r="D91" t="s">
-        <v>220</v>
+        <v>485</v>
       </c>
       <c r="E91" s="2">
-        <v>46155</v>
+        <v>46158</v>
       </c>
       <c r="F91" t="s">
-        <v>370</v>
+        <v>769</v>
       </c>
       <c r="G91" t="s">
-        <v>371</v>
+        <v>735</v>
       </c>
       <c r="H91" t="s">
-        <v>223</v>
+        <v>705</v>
       </c>
       <c r="I91" t="s">
-        <v>372</v>
+        <v>666</v>
       </c>
       <c r="J91" t="s">
-        <v>194</v>
-      </c>
-      <c r="K91" t="s">
-        <v>373</v>
-      </c>
-      <c r="L91" t="s">
-        <v>374</v>
+        <v>770</v>
       </c>
       <c r="M91" t="s">
-        <v>375</v>
+        <v>771</v>
       </c>
       <c r="N91" t="s">
-        <v>376</v>
+        <v>772</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>229</v>
+        <v>773</v>
       </c>
       <c r="B92" t="s">
-        <v>230</v>
+        <v>774</v>
       </c>
       <c r="C92" t="s">
-        <v>231</v>
+        <v>768</v>
       </c>
       <c r="D92" t="s">
-        <v>220</v>
+        <v>485</v>
       </c>
       <c r="E92" s="2">
-        <v>46139</v>
+        <v>46158</v>
       </c>
       <c r="F92" t="s">
-        <v>232</v>
+        <v>769</v>
       </c>
       <c r="G92" t="s">
-        <v>233</v>
+        <v>735</v>
       </c>
       <c r="H92" t="s">
-        <v>234</v>
+        <v>705</v>
       </c>
       <c r="I92" t="s">
-        <v>235</v>
+        <v>666</v>
       </c>
       <c r="J92" t="s">
-        <v>194</v>
-      </c>
-      <c r="K92" t="s">
-        <v>236</v>
-      </c>
-      <c r="L92" t="s">
-        <v>237</v>
+        <v>770</v>
       </c>
       <c r="M92" t="s">
-        <v>238</v>
+        <v>775</v>
       </c>
       <c r="N92" t="s">
-        <v>239</v>
+        <v>776</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>798</v>
+        <v>777</v>
       </c>
       <c r="B93" t="s">
-        <v>799</v>
+        <v>778</v>
       </c>
       <c r="C93" t="s">
-        <v>800</v>
+        <v>768</v>
       </c>
       <c r="D93" t="s">
-        <v>801</v>
+        <v>485</v>
       </c>
       <c r="E93" s="2">
-        <v>46126</v>
+        <v>46158</v>
       </c>
       <c r="F93" t="s">
-        <v>802</v>
+        <v>769</v>
       </c>
       <c r="G93" t="s">
-        <v>803</v>
+        <v>735</v>
       </c>
       <c r="H93" t="s">
-        <v>421</v>
+        <v>705</v>
       </c>
       <c r="I93" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J93" t="s">
-        <v>804</v>
-      </c>
-      <c r="L93" t="s">
-        <v>805</v>
+        <v>779</v>
       </c>
       <c r="M93" t="s">
-        <v>806</v>
+        <v>780</v>
+      </c>
+      <c r="N93" t="s">
+        <v>776</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>638</v>
+        <v>781</v>
       </c>
       <c r="B94" t="s">
-        <v>639</v>
+        <v>782</v>
       </c>
       <c r="C94" t="s">
-        <v>613</v>
+        <v>768</v>
       </c>
       <c r="D94" t="s">
-        <v>614</v>
+        <v>485</v>
       </c>
       <c r="E94" s="2">
-        <v>46189</v>
+        <v>46158</v>
       </c>
       <c r="F94" t="s">
-        <v>615</v>
+        <v>769</v>
       </c>
       <c r="G94" t="s">
-        <v>640</v>
+        <v>783</v>
       </c>
       <c r="H94" t="s">
-        <v>518</v>
+        <v>784</v>
       </c>
       <c r="I94" t="s">
-        <v>519</v>
+        <v>666</v>
       </c>
       <c r="J94" t="s">
-        <v>641</v>
-      </c>
-      <c r="K94" t="s">
-        <v>642</v>
+        <v>785</v>
       </c>
       <c r="L94" t="s">
-        <v>643</v>
+        <v>786</v>
       </c>
       <c r="M94" t="s">
-        <v>644</v>
+        <v>787</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>666</v>
+        <v>541</v>
       </c>
       <c r="B95" t="s">
-        <v>639</v>
+        <v>542</v>
       </c>
       <c r="C95" t="s">
-        <v>660</v>
+        <v>437</v>
       </c>
       <c r="D95" t="s">
-        <v>614</v>
+        <v>533</v>
       </c>
       <c r="E95" s="2">
-        <v>46189</v>
+        <v>46184</v>
       </c>
       <c r="F95" t="s">
-        <v>661</v>
+        <v>543</v>
       </c>
       <c r="G95" t="s">
-        <v>640</v>
+        <v>544</v>
       </c>
       <c r="H95" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="I95" t="s">
-        <v>667</v>
+        <v>545</v>
       </c>
       <c r="J95" t="s">
-        <v>668</v>
+        <v>546</v>
       </c>
       <c r="K95" t="s">
-        <v>669</v>
+        <v>547</v>
       </c>
       <c r="L95" t="s">
-        <v>670</v>
+        <v>548</v>
       </c>
       <c r="M95" t="s">
-        <v>671</v>
+        <v>549</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>396</v>
+        <v>435</v>
       </c>
       <c r="B96" t="s">
-        <v>397</v>
+        <v>436</v>
       </c>
       <c r="C96" t="s">
-        <v>387</v>
+        <v>437</v>
       </c>
       <c r="D96" t="s">
-        <v>319</v>
+        <v>284</v>
       </c>
       <c r="E96" s="2">
-        <v>46155</v>
+        <v>46176</v>
       </c>
       <c r="F96" t="s">
-        <v>388</v>
+        <v>438</v>
       </c>
       <c r="G96" t="s">
-        <v>397</v>
+        <v>439</v>
       </c>
       <c r="H96" t="s">
-        <v>390</v>
+        <v>430</v>
       </c>
       <c r="I96" t="s">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="J96" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K96" t="s">
-        <v>392</v>
+        <v>441</v>
       </c>
       <c r="L96" t="s">
-        <v>393</v>
+        <v>442</v>
       </c>
       <c r="M96" t="s">
-        <v>394</v>
+        <v>443</v>
       </c>
       <c r="N96" t="s">
-        <v>398</v>
+        <v>444</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>316</v>
+        <v>445</v>
       </c>
       <c r="B97" t="s">
-        <v>317</v>
+        <v>446</v>
       </c>
       <c r="C97" t="s">
-        <v>318</v>
+        <v>437</v>
       </c>
       <c r="D97" t="s">
-        <v>319</v>
+        <v>284</v>
       </c>
       <c r="E97" s="2">
-        <v>46151</v>
+        <v>46176</v>
       </c>
       <c r="F97" t="s">
-        <v>320</v>
+        <v>447</v>
       </c>
       <c r="G97" t="s">
-        <v>321</v>
+        <v>448</v>
       </c>
       <c r="H97" t="s">
-        <v>322</v>
+        <v>430</v>
       </c>
       <c r="I97" t="s">
-        <v>300</v>
+        <v>440</v>
       </c>
       <c r="J97" t="s">
-        <v>323</v>
+        <v>193</v>
       </c>
       <c r="K97" t="s">
-        <v>324</v>
+        <v>449</v>
       </c>
       <c r="L97" t="s">
-        <v>325</v>
+        <v>450</v>
       </c>
       <c r="M97" t="s">
-        <v>326</v>
+        <v>451</v>
       </c>
       <c r="N97" t="s">
-        <v>327</v>
+        <v>452</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>70</v>
+        <v>531</v>
       </c>
       <c r="B98" t="s">
-        <v>71</v>
+        <v>532</v>
       </c>
       <c r="C98" t="s">
-        <v>55</v>
+        <v>437</v>
       </c>
       <c r="D98" t="s">
-        <v>72</v>
+        <v>533</v>
       </c>
       <c r="E98" s="2">
-        <v>46112</v>
+        <v>46184</v>
       </c>
       <c r="F98" t="s">
-        <v>73</v>
+        <v>534</v>
       </c>
       <c r="G98" t="s">
-        <v>74</v>
+        <v>535</v>
       </c>
       <c r="H98" t="s">
-        <v>58</v>
+        <v>536</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
+        <v>518</v>
       </c>
       <c r="J98" t="s">
-        <v>75</v>
+        <v>537</v>
       </c>
       <c r="K98" t="s">
-        <v>76</v>
+        <v>538</v>
       </c>
       <c r="L98" t="s">
-        <v>77</v>
+        <v>539</v>
       </c>
       <c r="M98" t="s">
-        <v>62</v>
+        <v>540</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>97</v>
+        <v>626</v>
       </c>
       <c r="B99" t="s">
-        <v>98</v>
+        <v>627</v>
       </c>
       <c r="C99" t="s">
-        <v>55</v>
+        <v>612</v>
       </c>
       <c r="D99" t="s">
-        <v>86</v>
+        <v>613</v>
       </c>
       <c r="E99" s="2">
-        <v>46112</v>
+        <v>46189</v>
       </c>
       <c r="F99" t="s">
-        <v>73</v>
+        <v>614</v>
       </c>
       <c r="G99" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="H99" t="s">
-        <v>58</v>
+        <v>517</v>
       </c>
       <c r="I99" t="s">
-        <v>19</v>
+        <v>518</v>
       </c>
       <c r="J99" t="s">
-        <v>100</v>
+        <v>628</v>
       </c>
       <c r="K99" t="s">
-        <v>101</v>
+        <v>629</v>
       </c>
       <c r="L99" t="s">
-        <v>102</v>
+        <v>630</v>
       </c>
       <c r="M99" t="s">
-        <v>62</v>
+        <v>631</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>91</v>
+        <v>651</v>
       </c>
       <c r="B100" t="s">
-        <v>92</v>
+        <v>652</v>
       </c>
       <c r="C100" t="s">
-        <v>55</v>
+        <v>612</v>
       </c>
       <c r="D100" t="s">
-        <v>86</v>
+        <v>613</v>
       </c>
       <c r="E100" s="2">
-        <v>46112</v>
+        <v>46189</v>
       </c>
       <c r="F100" t="s">
-        <v>73</v>
+        <v>614</v>
       </c>
       <c r="G100" t="s">
-        <v>93</v>
+        <v>653</v>
       </c>
       <c r="H100" t="s">
-        <v>58</v>
+        <v>517</v>
       </c>
       <c r="I100" t="s">
-        <v>19</v>
+        <v>518</v>
       </c>
       <c r="J100" t="s">
-        <v>94</v>
+        <v>654</v>
       </c>
       <c r="K100" t="s">
-        <v>95</v>
+        <v>655</v>
       </c>
       <c r="L100" t="s">
-        <v>96</v>
+        <v>656</v>
       </c>
       <c r="M100" t="s">
-        <v>62</v>
+        <v>657</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>579</v>
+        <v>644</v>
       </c>
       <c r="B101" t="s">
-        <v>580</v>
+        <v>645</v>
       </c>
       <c r="C101" t="s">
-        <v>581</v>
+        <v>612</v>
       </c>
       <c r="D101" t="s">
-        <v>571</v>
+        <v>613</v>
       </c>
       <c r="E101" s="2">
-        <v>46184</v>
+        <v>46189</v>
       </c>
       <c r="F101" t="s">
-        <v>582</v>
+        <v>614</v>
       </c>
       <c r="G101" t="s">
-        <v>583</v>
+        <v>646</v>
       </c>
       <c r="H101" t="s">
-        <v>584</v>
+        <v>517</v>
       </c>
       <c r="I101" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J101" t="s">
-        <v>585</v>
+        <v>647</v>
       </c>
       <c r="K101" t="s">
-        <v>586</v>
+        <v>648</v>
       </c>
       <c r="L101" t="s">
-        <v>587</v>
+        <v>649</v>
       </c>
       <c r="M101" t="s">
-        <v>588</v>
+        <v>650</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>84</v>
+        <v>632</v>
       </c>
       <c r="B102" t="s">
-        <v>85</v>
+        <v>633</v>
       </c>
       <c r="C102" t="s">
-        <v>55</v>
+        <v>612</v>
       </c>
       <c r="D102" t="s">
-        <v>86</v>
+        <v>613</v>
       </c>
       <c r="E102" s="2">
-        <v>46112</v>
+        <v>46189</v>
       </c>
       <c r="F102" t="s">
-        <v>73</v>
+        <v>614</v>
       </c>
       <c r="G102" t="s">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="H102" t="s">
-        <v>58</v>
+        <v>517</v>
       </c>
       <c r="I102" t="s">
-        <v>19</v>
+        <v>518</v>
       </c>
       <c r="J102" t="s">
-        <v>88</v>
+        <v>634</v>
       </c>
       <c r="K102" t="s">
-        <v>89</v>
+        <v>629</v>
       </c>
       <c r="L102" t="s">
-        <v>90</v>
+        <v>635</v>
       </c>
       <c r="M102" t="s">
-        <v>62</v>
+        <v>636</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>78</v>
+        <v>610</v>
       </c>
       <c r="B103" t="s">
-        <v>79</v>
+        <v>611</v>
       </c>
       <c r="C103" t="s">
-        <v>55</v>
+        <v>612</v>
       </c>
       <c r="D103" t="s">
-        <v>72</v>
+        <v>613</v>
       </c>
       <c r="E103" s="2">
-        <v>46112</v>
+        <v>46189</v>
       </c>
       <c r="F103" t="s">
-        <v>73</v>
+        <v>614</v>
       </c>
       <c r="G103" t="s">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="H103" t="s">
-        <v>58</v>
+        <v>517</v>
       </c>
       <c r="I103" t="s">
-        <v>19</v>
+        <v>518</v>
       </c>
       <c r="J103" t="s">
-        <v>81</v>
+        <v>615</v>
       </c>
       <c r="K103" t="s">
-        <v>82</v>
+        <v>616</v>
       </c>
       <c r="L103" t="s">
-        <v>83</v>
+        <v>617</v>
       </c>
       <c r="M103" t="s">
-        <v>62</v>
+        <v>618</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>860</v>
+        <v>619</v>
       </c>
       <c r="B104" t="s">
-        <v>851</v>
+        <v>620</v>
       </c>
       <c r="C104" t="s">
-        <v>852</v>
+        <v>612</v>
       </c>
       <c r="D104" t="s">
-        <v>15</v>
-      </c>
-      <c r="E104" s="3">
-        <v>46133</v>
+        <v>613</v>
+      </c>
+      <c r="E104" s="2">
+        <v>46189</v>
       </c>
       <c r="F104" t="s">
-        <v>853</v>
+        <v>614</v>
       </c>
       <c r="G104" t="s">
-        <v>854</v>
+        <v>621</v>
       </c>
       <c r="H104" t="s">
-        <v>855</v>
+        <v>517</v>
       </c>
       <c r="I104" t="s">
-        <v>19</v>
+        <v>518</v>
       </c>
       <c r="J104" t="s">
-        <v>856</v>
+        <v>622</v>
       </c>
       <c r="K104" t="s">
-        <v>857</v>
+        <v>623</v>
       </c>
       <c r="L104" t="s">
-        <v>858</v>
+        <v>624</v>
       </c>
       <c r="M104" t="s">
-        <v>859</v>
+        <v>625</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>868</v>
+        <v>637</v>
       </c>
       <c r="B105" t="s">
-        <v>862</v>
+        <v>638</v>
       </c>
       <c r="C105" t="s">
-        <v>155</v>
+        <v>612</v>
       </c>
       <c r="D105" t="s">
-        <v>15</v>
-      </c>
-      <c r="E105" s="3">
-        <v>46159</v>
+        <v>613</v>
+      </c>
+      <c r="E105" s="2">
+        <v>46189</v>
       </c>
       <c r="F105" t="s">
-        <v>762</v>
+        <v>614</v>
       </c>
       <c r="G105" t="s">
-        <v>854</v>
+        <v>639</v>
       </c>
       <c r="H105" t="s">
-        <v>863</v>
+        <v>517</v>
       </c>
       <c r="I105" t="s">
-        <v>19</v>
+        <v>518</v>
       </c>
       <c r="J105" t="s">
-        <v>864</v>
+        <v>640</v>
       </c>
       <c r="K105" t="s">
-        <v>865</v>
+        <v>641</v>
       </c>
       <c r="L105" t="s">
-        <v>866</v>
+        <v>642</v>
       </c>
       <c r="M105" t="s">
-        <v>867</v>
+        <v>643</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>878</v>
+        <v>493</v>
       </c>
       <c r="B106" t="s">
-        <v>869</v>
+        <v>494</v>
       </c>
       <c r="C106" t="s">
-        <v>870</v>
+        <v>495</v>
       </c>
       <c r="D106" t="s">
-        <v>871</v>
-      </c>
-      <c r="E106" s="3">
-        <v>46387</v>
+        <v>496</v>
+      </c>
+      <c r="E106" s="2">
+        <v>46165</v>
       </c>
       <c r="F106" t="s">
-        <v>872</v>
+        <v>497</v>
       </c>
       <c r="G106" t="s">
-        <v>854</v>
+        <v>494</v>
       </c>
       <c r="H106" t="s">
-        <v>873</v>
+        <v>498</v>
       </c>
       <c r="I106" t="s">
-        <v>19</v>
+        <v>499</v>
       </c>
       <c r="J106" t="s">
-        <v>874</v>
+        <v>193</v>
       </c>
       <c r="K106" t="s">
-        <v>875</v>
+        <v>500</v>
       </c>
       <c r="L106" t="s">
-        <v>876</v>
+        <v>501</v>
       </c>
       <c r="M106" t="s">
-        <v>877</v>
+        <v>502</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>890</v>
+        <v>848</v>
       </c>
       <c r="B107" t="s">
-        <v>880</v>
+        <v>839</v>
       </c>
       <c r="C107" t="s">
-        <v>881</v>
+        <v>840</v>
       </c>
       <c r="D107" t="s">
-        <v>882</v>
+        <v>841</v>
       </c>
       <c r="E107" s="3">
-        <v>46204</v>
+        <v>46189</v>
       </c>
       <c r="F107" t="s">
-        <v>883</v>
+        <v>842</v>
       </c>
       <c r="G107" t="s">
-        <v>854</v>
+        <v>843</v>
       </c>
       <c r="H107" t="s">
-        <v>884</v>
+        <v>421</v>
       </c>
       <c r="I107" t="s">
-        <v>885</v>
+        <v>844</v>
       </c>
       <c r="J107" t="s">
-        <v>886</v>
+        <v>845</v>
       </c>
       <c r="K107" t="s">
-        <v>887</v>
+        <v>846</v>
       </c>
       <c r="L107" t="s">
-        <v>888</v>
-      </c>
-      <c r="M107" t="s">
-        <v>889</v>
+        <v>847</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>900</v>
+        <v>691</v>
       </c>
       <c r="B108" t="s">
-        <v>891</v>
+        <v>692</v>
       </c>
       <c r="C108" t="s">
-        <v>892</v>
+        <v>693</v>
       </c>
       <c r="D108" t="s">
-        <v>893</v>
-      </c>
-      <c r="E108" s="3">
-        <v>46204</v>
+        <v>485</v>
+      </c>
+      <c r="E108" s="2">
+        <v>46118</v>
       </c>
       <c r="F108" t="s">
-        <v>894</v>
+        <v>694</v>
       </c>
       <c r="G108" t="s">
-        <v>854</v>
+        <v>678</v>
       </c>
       <c r="H108" t="s">
-        <v>895</v>
+        <v>695</v>
       </c>
       <c r="I108" t="s">
-        <v>19</v>
+        <v>666</v>
       </c>
       <c r="J108" t="s">
-        <v>896</v>
+        <v>696</v>
       </c>
       <c r="K108" t="s">
-        <v>897</v>
+        <v>697</v>
       </c>
       <c r="L108" t="s">
-        <v>898</v>
+        <v>698</v>
       </c>
       <c r="M108" t="s">
-        <v>899</v>
+        <v>699</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>911</v>
+        <v>269</v>
       </c>
       <c r="B109" t="s">
-        <v>901</v>
+        <v>270</v>
       </c>
       <c r="C109" t="s">
-        <v>902</v>
+        <v>271</v>
       </c>
       <c r="D109" t="s">
-        <v>903</v>
-      </c>
-      <c r="E109" s="3">
+        <v>272</v>
+      </c>
+      <c r="E109" s="2">
         <v>46142</v>
       </c>
       <c r="F109" t="s">
-        <v>904</v>
+        <v>273</v>
       </c>
       <c r="G109" t="s">
-        <v>905</v>
+        <v>274</v>
       </c>
       <c r="H109" t="s">
-        <v>826</v>
+        <v>275</v>
       </c>
       <c r="I109" t="s">
-        <v>906</v>
+        <v>276</v>
       </c>
       <c r="J109" t="s">
-        <v>907</v>
+        <v>193</v>
       </c>
       <c r="K109" t="s">
-        <v>908</v>
+        <v>277</v>
       </c>
       <c r="L109" t="s">
-        <v>909</v>
+        <v>278</v>
       </c>
       <c r="M109" t="s">
-        <v>910</v>
+        <v>279</v>
+      </c>
+      <c r="N109" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>921</v>
+        <v>464</v>
       </c>
       <c r="B110" t="s">
-        <v>912</v>
+        <v>465</v>
       </c>
       <c r="C110" t="s">
-        <v>913</v>
+        <v>466</v>
       </c>
       <c r="D110" t="s">
-        <v>914</v>
-      </c>
-      <c r="E110" s="3">
-        <v>46162</v>
+        <v>208</v>
+      </c>
+      <c r="E110" s="2">
+        <v>46173</v>
       </c>
       <c r="F110" t="s">
-        <v>915</v>
+        <v>467</v>
       </c>
       <c r="G110" t="s">
-        <v>667</v>
+        <v>465</v>
       </c>
       <c r="H110" t="s">
-        <v>916</v>
+        <v>468</v>
       </c>
       <c r="I110" t="s">
-        <v>885</v>
+        <v>469</v>
       </c>
       <c r="J110" t="s">
-        <v>917</v>
+        <v>193</v>
       </c>
       <c r="K110" t="s">
-        <v>918</v>
+        <v>470</v>
       </c>
       <c r="L110" t="s">
-        <v>919</v>
+        <v>471</v>
       </c>
       <c r="M110" t="s">
-        <v>920</v>
+        <v>472</v>
+      </c>
+      <c r="N110" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>931</v>
+        <v>474</v>
       </c>
       <c r="B111" t="s">
-        <v>922</v>
+        <v>475</v>
       </c>
       <c r="C111" t="s">
-        <v>923</v>
+        <v>466</v>
       </c>
       <c r="D111" t="s">
-        <v>924</v>
-      </c>
-      <c r="E111" s="3">
+        <v>208</v>
+      </c>
+      <c r="E111" s="2">
         <v>46173</v>
       </c>
       <c r="F111" t="s">
-        <v>925</v>
+        <v>476</v>
       </c>
       <c r="G111" t="s">
-        <v>667</v>
+        <v>475</v>
       </c>
       <c r="H111" t="s">
-        <v>926</v>
+        <v>477</v>
       </c>
       <c r="I111" t="s">
-        <v>885</v>
+        <v>478</v>
       </c>
       <c r="J111" t="s">
-        <v>927</v>
+        <v>193</v>
       </c>
       <c r="K111" t="s">
-        <v>928</v>
+        <v>479</v>
       </c>
       <c r="L111" t="s">
-        <v>929</v>
+        <v>480</v>
       </c>
       <c r="M111" t="s">
-        <v>930</v>
+        <v>481</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>940</v>
+        <v>1039</v>
       </c>
       <c r="B112" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D112" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E112" s="3">
+        <v>46226</v>
+      </c>
+      <c r="F112" t="s">
+        <v>55</v>
+      </c>
+      <c r="G112" t="s">
+        <v>666</v>
+      </c>
+      <c r="H112" t="s">
+        <v>1034</v>
+      </c>
+      <c r="I112" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J112" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K112" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L112" t="s">
+        <v>1037</v>
+      </c>
+      <c r="M112" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D113" t="s">
+        <v>998</v>
+      </c>
+      <c r="E113" s="3">
+        <v>46226</v>
+      </c>
+      <c r="F113" t="s">
+        <v>55</v>
+      </c>
+      <c r="G113" t="s">
+        <v>666</v>
+      </c>
+      <c r="H113" t="s">
+        <v>1041</v>
+      </c>
+      <c r="I113" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J113" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K113" t="s">
+        <v>1043</v>
+      </c>
+      <c r="L113" t="s">
+        <v>1044</v>
+      </c>
+      <c r="M113" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>599</v>
+      </c>
+      <c r="B114" t="s">
+        <v>600</v>
+      </c>
+      <c r="C114" t="s">
+        <v>601</v>
+      </c>
+      <c r="D114" t="s">
+        <v>602</v>
+      </c>
+      <c r="E114" s="2">
+        <v>46187</v>
+      </c>
+      <c r="F114" t="s">
+        <v>603</v>
+      </c>
+      <c r="G114" t="s">
+        <v>328</v>
+      </c>
+      <c r="H114" t="s">
+        <v>604</v>
+      </c>
+      <c r="I114" t="s">
+        <v>605</v>
+      </c>
+      <c r="J114" t="s">
+        <v>606</v>
+      </c>
+      <c r="K114" t="s">
+        <v>607</v>
+      </c>
+      <c r="L114" t="s">
+        <v>608</v>
+      </c>
+      <c r="M114" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>939</v>
+      </c>
+      <c r="B115" t="s">
+        <v>931</v>
+      </c>
+      <c r="C115" t="s">
         <v>932</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D115" t="s">
+        <v>913</v>
+      </c>
+      <c r="E115" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F115" t="s">
         <v>933</v>
       </c>
-      <c r="D112" t="s">
-        <v>914</v>
-      </c>
-      <c r="E112" s="3">
+      <c r="G115" t="s">
+        <v>666</v>
+      </c>
+      <c r="H115" t="s">
+        <v>934</v>
+      </c>
+      <c r="I115" t="s">
+        <v>884</v>
+      </c>
+      <c r="J115" t="s">
+        <v>935</v>
+      </c>
+      <c r="K115" t="s">
+        <v>936</v>
+      </c>
+      <c r="L115" t="s">
+        <v>937</v>
+      </c>
+      <c r="M115" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D116" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E116" s="3">
+        <v>46164</v>
+      </c>
+      <c r="F116" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G116" t="s">
+        <v>666</v>
+      </c>
+      <c r="H116" t="s">
+        <v>1062</v>
+      </c>
+      <c r="I116" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J116" t="s">
+        <v>1063</v>
+      </c>
+      <c r="K116" t="s">
+        <v>1064</v>
+      </c>
+      <c r="L116" t="s">
+        <v>1065</v>
+      </c>
+      <c r="M116" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>281</v>
+      </c>
+      <c r="B117" t="s">
+        <v>282</v>
+      </c>
+      <c r="C117" t="s">
+        <v>283</v>
+      </c>
+      <c r="D117" t="s">
+        <v>284</v>
+      </c>
+      <c r="E117" s="2">
+        <v>46146</v>
+      </c>
+      <c r="F117" t="s">
+        <v>285</v>
+      </c>
+      <c r="G117" t="s">
+        <v>286</v>
+      </c>
+      <c r="H117" t="s">
+        <v>287</v>
+      </c>
+      <c r="I117" t="s">
+        <v>288</v>
+      </c>
+      <c r="J117" t="s">
+        <v>193</v>
+      </c>
+      <c r="K117" t="s">
+        <v>289</v>
+      </c>
+      <c r="L117" t="s">
+        <v>290</v>
+      </c>
+      <c r="M117" t="s">
+        <v>291</v>
+      </c>
+      <c r="N117" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>567</v>
+      </c>
+      <c r="B118" t="s">
+        <v>568</v>
+      </c>
+      <c r="C118" t="s">
+        <v>569</v>
+      </c>
+      <c r="D118" t="s">
+        <v>570</v>
+      </c>
+      <c r="E118" s="2">
+        <v>46184</v>
+      </c>
+      <c r="F118" t="s">
+        <v>571</v>
+      </c>
+      <c r="G118" t="s">
+        <v>572</v>
+      </c>
+      <c r="H118" t="s">
+        <v>573</v>
+      </c>
+      <c r="I118" t="s">
+        <v>518</v>
+      </c>
+      <c r="J118" t="s">
+        <v>574</v>
+      </c>
+      <c r="K118" t="s">
+        <v>575</v>
+      </c>
+      <c r="L118" t="s">
+        <v>576</v>
+      </c>
+      <c r="M118" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>578</v>
+      </c>
+      <c r="B119" t="s">
+        <v>579</v>
+      </c>
+      <c r="C119" t="s">
+        <v>580</v>
+      </c>
+      <c r="D119" t="s">
+        <v>570</v>
+      </c>
+      <c r="E119" s="2">
+        <v>46184</v>
+      </c>
+      <c r="F119" t="s">
+        <v>581</v>
+      </c>
+      <c r="G119" t="s">
+        <v>582</v>
+      </c>
+      <c r="H119" t="s">
+        <v>583</v>
+      </c>
+      <c r="I119" t="s">
+        <v>518</v>
+      </c>
+      <c r="J119" t="s">
+        <v>584</v>
+      </c>
+      <c r="K119" t="s">
+        <v>585</v>
+      </c>
+      <c r="L119" t="s">
+        <v>586</v>
+      </c>
+      <c r="M119" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>62</v>
+      </c>
+      <c r="B120" t="s">
+        <v>63</v>
+      </c>
+      <c r="C120" t="s">
+        <v>54</v>
+      </c>
+      <c r="D120" t="s">
+        <v>14</v>
+      </c>
+      <c r="E120" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F120" t="s">
+        <v>55</v>
+      </c>
+      <c r="G120" t="s">
+        <v>64</v>
+      </c>
+      <c r="H120" t="s">
+        <v>57</v>
+      </c>
+      <c r="I120" t="s">
+        <v>18</v>
+      </c>
+      <c r="J120" t="s">
+        <v>65</v>
+      </c>
+      <c r="K120" t="s">
+        <v>66</v>
+      </c>
+      <c r="L120" t="s">
+        <v>67</v>
+      </c>
+      <c r="M120" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>52</v>
+      </c>
+      <c r="B121" t="s">
+        <v>53</v>
+      </c>
+      <c r="C121" t="s">
+        <v>54</v>
+      </c>
+      <c r="D121" t="s">
+        <v>14</v>
+      </c>
+      <c r="E121" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F121" t="s">
+        <v>55</v>
+      </c>
+      <c r="G121" t="s">
+        <v>56</v>
+      </c>
+      <c r="H121" t="s">
+        <v>57</v>
+      </c>
+      <c r="I121" t="s">
+        <v>18</v>
+      </c>
+      <c r="J121" t="s">
+        <v>58</v>
+      </c>
+      <c r="K121" t="s">
+        <v>59</v>
+      </c>
+      <c r="L121" t="s">
+        <v>60</v>
+      </c>
+      <c r="M121" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>69</v>
+      </c>
+      <c r="B122" t="s">
+        <v>70</v>
+      </c>
+      <c r="C122" t="s">
+        <v>54</v>
+      </c>
+      <c r="D122" t="s">
+        <v>71</v>
+      </c>
+      <c r="E122" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F122" t="s">
+        <v>72</v>
+      </c>
+      <c r="G122" t="s">
+        <v>73</v>
+      </c>
+      <c r="H122" t="s">
+        <v>57</v>
+      </c>
+      <c r="I122" t="s">
+        <v>18</v>
+      </c>
+      <c r="J122" t="s">
+        <v>74</v>
+      </c>
+      <c r="K122" t="s">
+        <v>75</v>
+      </c>
+      <c r="L122" t="s">
+        <v>76</v>
+      </c>
+      <c r="M122" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>96</v>
+      </c>
+      <c r="B123" t="s">
+        <v>97</v>
+      </c>
+      <c r="C123" t="s">
+        <v>54</v>
+      </c>
+      <c r="D123" t="s">
+        <v>85</v>
+      </c>
+      <c r="E123" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F123" t="s">
+        <v>72</v>
+      </c>
+      <c r="G123" t="s">
+        <v>98</v>
+      </c>
+      <c r="H123" t="s">
+        <v>57</v>
+      </c>
+      <c r="I123" t="s">
+        <v>18</v>
+      </c>
+      <c r="J123" t="s">
+        <v>99</v>
+      </c>
+      <c r="K123" t="s">
+        <v>100</v>
+      </c>
+      <c r="L123" t="s">
+        <v>101</v>
+      </c>
+      <c r="M123" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>90</v>
+      </c>
+      <c r="B124" t="s">
+        <v>91</v>
+      </c>
+      <c r="C124" t="s">
+        <v>54</v>
+      </c>
+      <c r="D124" t="s">
+        <v>85</v>
+      </c>
+      <c r="E124" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F124" t="s">
+        <v>72</v>
+      </c>
+      <c r="G124" t="s">
+        <v>92</v>
+      </c>
+      <c r="H124" t="s">
+        <v>57</v>
+      </c>
+      <c r="I124" t="s">
+        <v>18</v>
+      </c>
+      <c r="J124" t="s">
+        <v>93</v>
+      </c>
+      <c r="K124" t="s">
+        <v>94</v>
+      </c>
+      <c r="L124" t="s">
+        <v>95</v>
+      </c>
+      <c r="M124" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>83</v>
+      </c>
+      <c r="B125" t="s">
+        <v>84</v>
+      </c>
+      <c r="C125" t="s">
+        <v>54</v>
+      </c>
+      <c r="D125" t="s">
+        <v>85</v>
+      </c>
+      <c r="E125" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F125" t="s">
+        <v>72</v>
+      </c>
+      <c r="G125" t="s">
+        <v>86</v>
+      </c>
+      <c r="H125" t="s">
+        <v>57</v>
+      </c>
+      <c r="I125" t="s">
+        <v>18</v>
+      </c>
+      <c r="J125" t="s">
+        <v>87</v>
+      </c>
+      <c r="K125" t="s">
+        <v>88</v>
+      </c>
+      <c r="L125" t="s">
+        <v>89</v>
+      </c>
+      <c r="M125" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>77</v>
+      </c>
+      <c r="B126" t="s">
+        <v>78</v>
+      </c>
+      <c r="C126" t="s">
+        <v>54</v>
+      </c>
+      <c r="D126" t="s">
+        <v>71</v>
+      </c>
+      <c r="E126" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F126" t="s">
+        <v>72</v>
+      </c>
+      <c r="G126" t="s">
+        <v>79</v>
+      </c>
+      <c r="H126" t="s">
+        <v>57</v>
+      </c>
+      <c r="I126" t="s">
+        <v>18</v>
+      </c>
+      <c r="J126" t="s">
+        <v>80</v>
+      </c>
+      <c r="K126" t="s">
+        <v>81</v>
+      </c>
+      <c r="L126" t="s">
+        <v>82</v>
+      </c>
+      <c r="M126" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D127" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E127" s="3">
+        <v>46188</v>
+      </c>
+      <c r="F127" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G127" t="s">
+        <v>666</v>
+      </c>
+      <c r="H127" t="s">
+        <v>1074</v>
+      </c>
+      <c r="I127" t="s">
+        <v>1067</v>
+      </c>
+      <c r="J127" t="s">
+        <v>1075</v>
+      </c>
+      <c r="K127" t="s">
+        <v>1076</v>
+      </c>
+      <c r="L127" t="s">
+        <v>1077</v>
+      </c>
+      <c r="M127" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B128" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C128" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D128" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E128" s="3">
+        <v>46188</v>
+      </c>
+      <c r="F128" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G128" t="s">
+        <v>666</v>
+      </c>
+      <c r="H128" t="s">
+        <v>1080</v>
+      </c>
+      <c r="I128" t="s">
+        <v>1067</v>
+      </c>
+      <c r="J128" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K128" t="s">
+        <v>1082</v>
+      </c>
+      <c r="L128" t="s">
+        <v>1083</v>
+      </c>
+      <c r="M128" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D129" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E129" s="3">
+        <v>46188</v>
+      </c>
+      <c r="F129" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G129" t="s">
+        <v>666</v>
+      </c>
+      <c r="H129" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I129" t="s">
+        <v>1067</v>
+      </c>
+      <c r="J129" t="s">
+        <v>1075</v>
+      </c>
+      <c r="K129" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L129" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M129" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B130" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D130" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E130" s="3">
+        <v>46188</v>
+      </c>
+      <c r="F130" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G130" t="s">
+        <v>666</v>
+      </c>
+      <c r="H130" t="s">
+        <v>1093</v>
+      </c>
+      <c r="I130" t="s">
+        <v>1067</v>
+      </c>
+      <c r="J130" t="s">
+        <v>1094</v>
+      </c>
+      <c r="K130" t="s">
+        <v>1095</v>
+      </c>
+      <c r="L130" t="s">
+        <v>1096</v>
+      </c>
+      <c r="M130" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B131" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D131" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E131" s="3">
+        <v>46188</v>
+      </c>
+      <c r="F131" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G131" t="s">
+        <v>666</v>
+      </c>
+      <c r="H131" t="s">
+        <v>1100</v>
+      </c>
+      <c r="I131" t="s">
+        <v>1067</v>
+      </c>
+      <c r="J131" t="s">
+        <v>1075</v>
+      </c>
+      <c r="K131" t="s">
+        <v>1101</v>
+      </c>
+      <c r="L131" t="s">
+        <v>1102</v>
+      </c>
+      <c r="M131" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B132" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D132" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E132" s="3">
+        <v>46157</v>
+      </c>
+      <c r="F132" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G132" t="s">
+        <v>666</v>
+      </c>
+      <c r="H132" t="s">
+        <v>1107</v>
+      </c>
+      <c r="I132" t="s">
+        <v>1067</v>
+      </c>
+      <c r="J132" t="s">
+        <v>1108</v>
+      </c>
+      <c r="K132" t="s">
+        <v>1109</v>
+      </c>
+      <c r="L132" t="s">
+        <v>1110</v>
+      </c>
+      <c r="M132" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D133" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E133" s="3">
+        <v>46188</v>
+      </c>
+      <c r="F133" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G133" t="s">
+        <v>666</v>
+      </c>
+      <c r="H133" t="s">
+        <v>1114</v>
+      </c>
+      <c r="I133" t="s">
+        <v>1067</v>
+      </c>
+      <c r="J133" t="s">
+        <v>1115</v>
+      </c>
+      <c r="K133" t="s">
+        <v>1116</v>
+      </c>
+      <c r="L133" t="s">
+        <v>1117</v>
+      </c>
+      <c r="M133" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C134" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D134" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E134" s="3">
+        <v>46188</v>
+      </c>
+      <c r="F134" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G134" t="s">
+        <v>666</v>
+      </c>
+      <c r="H134" t="s">
+        <v>1121</v>
+      </c>
+      <c r="I134" t="s">
+        <v>1067</v>
+      </c>
+      <c r="J134" t="s">
+        <v>1122</v>
+      </c>
+      <c r="K134" t="s">
+        <v>1123</v>
+      </c>
+      <c r="L134" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M134" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C135" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D135" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E135" s="3">
+        <v>46188</v>
+      </c>
+      <c r="F135" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G135" t="s">
+        <v>666</v>
+      </c>
+      <c r="H135" t="s">
+        <v>1128</v>
+      </c>
+      <c r="I135" t="s">
+        <v>1067</v>
+      </c>
+      <c r="J135" t="s">
+        <v>1129</v>
+      </c>
+      <c r="K135" t="s">
+        <v>1130</v>
+      </c>
+      <c r="L135" t="s">
+        <v>1131</v>
+      </c>
+      <c r="M135" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C136" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D136" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E136" s="3">
+        <v>46188</v>
+      </c>
+      <c r="F136" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G136" t="s">
+        <v>666</v>
+      </c>
+      <c r="H136" t="s">
+        <v>1135</v>
+      </c>
+      <c r="I136" t="s">
+        <v>1067</v>
+      </c>
+      <c r="J136" t="s">
+        <v>1136</v>
+      </c>
+      <c r="K136" t="s">
+        <v>1137</v>
+      </c>
+      <c r="L136" t="s">
+        <v>1138</v>
+      </c>
+      <c r="M136" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B137" t="s">
+        <v>123</v>
+      </c>
+      <c r="C137" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D137" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E137" s="3">
         <v>46203</v>
       </c>
-      <c r="F112" t="s">
-        <v>934</v>
-      </c>
-      <c r="G112" t="s">
-        <v>667</v>
-      </c>
-      <c r="H112" t="s">
-        <v>935</v>
-      </c>
-      <c r="I112" t="s">
-        <v>885</v>
-      </c>
-      <c r="J112" t="s">
-        <v>936</v>
-      </c>
-      <c r="K112" t="s">
-        <v>937</v>
-      </c>
-      <c r="L112" t="s">
-        <v>938</v>
-      </c>
-      <c r="M112" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>949</v>
-      </c>
-      <c r="B113" t="s">
-        <v>941</v>
-      </c>
-      <c r="C113" t="s">
-        <v>942</v>
-      </c>
-      <c r="D113" t="s">
-        <v>914</v>
-      </c>
-      <c r="E113" s="3">
-        <v>46212</v>
-      </c>
-      <c r="F113" t="s">
-        <v>943</v>
-      </c>
-      <c r="G113" t="s">
-        <v>667</v>
-      </c>
-      <c r="H113" t="s">
-        <v>944</v>
-      </c>
-      <c r="I113" t="s">
-        <v>885</v>
-      </c>
-      <c r="J113" t="s">
-        <v>945</v>
-      </c>
-      <c r="K113" t="s">
-        <v>946</v>
-      </c>
-      <c r="L113" t="s">
-        <v>947</v>
-      </c>
-      <c r="M113" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>959</v>
-      </c>
-      <c r="B114" t="s">
-        <v>950</v>
-      </c>
-      <c r="C114" t="s">
-        <v>951</v>
-      </c>
-      <c r="D114" t="s">
+      <c r="F137" t="s">
         <v>952</v>
       </c>
-      <c r="E114" s="3">
-        <v>46152</v>
-      </c>
-      <c r="F114" t="s">
-        <v>953</v>
-      </c>
-      <c r="G114" t="s">
-        <v>667</v>
-      </c>
-      <c r="H114" t="s">
-        <v>954</v>
-      </c>
-      <c r="I114" t="s">
-        <v>885</v>
-      </c>
-      <c r="J114" t="s">
-        <v>955</v>
-      </c>
-      <c r="K114" t="s">
-        <v>956</v>
-      </c>
-      <c r="L114" t="s">
-        <v>957</v>
-      </c>
-      <c r="M114" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>968</v>
-      </c>
-      <c r="B115" t="s">
-        <v>960</v>
-      </c>
-      <c r="C115" t="s">
-        <v>961</v>
-      </c>
-      <c r="D115" t="s">
-        <v>614</v>
-      </c>
-      <c r="E115" s="3">
-        <v>46173</v>
-      </c>
-      <c r="F115" t="s">
-        <v>962</v>
-      </c>
-      <c r="G115" t="s">
-        <v>667</v>
-      </c>
-      <c r="H115" t="s">
-        <v>963</v>
-      </c>
-      <c r="I115" t="s">
-        <v>885</v>
-      </c>
-      <c r="J115" t="s">
-        <v>964</v>
-      </c>
-      <c r="K115" t="s">
-        <v>965</v>
-      </c>
-      <c r="L115" t="s">
-        <v>966</v>
-      </c>
-      <c r="M115" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>977</v>
-      </c>
-      <c r="B116" t="s">
-        <v>969</v>
-      </c>
-      <c r="C116" t="s">
-        <v>970</v>
-      </c>
-      <c r="D116" t="s">
-        <v>515</v>
-      </c>
-      <c r="E116" s="3">
-        <v>46173</v>
-      </c>
-      <c r="F116" t="s">
-        <v>971</v>
-      </c>
-      <c r="G116" t="s">
-        <v>667</v>
-      </c>
-      <c r="H116" t="s">
-        <v>972</v>
-      </c>
-      <c r="I116" t="s">
-        <v>885</v>
-      </c>
-      <c r="J116" t="s">
-        <v>973</v>
-      </c>
-      <c r="K116" t="s">
-        <v>974</v>
-      </c>
-      <c r="L116" t="s">
-        <v>975</v>
-      </c>
-      <c r="M116" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>986</v>
-      </c>
-      <c r="B117" t="s">
-        <v>147</v>
-      </c>
-      <c r="C117" t="s">
-        <v>978</v>
-      </c>
-      <c r="D117" t="s">
-        <v>979</v>
-      </c>
-      <c r="E117" s="3">
+      <c r="G137" t="s">
+        <v>666</v>
+      </c>
+      <c r="H137" t="s">
+        <v>126</v>
+      </c>
+      <c r="I137" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J137" t="s">
+        <v>1143</v>
+      </c>
+      <c r="K137" t="s">
+        <v>1144</v>
+      </c>
+      <c r="L137" t="s">
+        <v>1145</v>
+      </c>
+      <c r="M137" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C138" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D138" t="s">
+        <v>272</v>
+      </c>
+      <c r="E138" s="3">
+        <v>46167</v>
+      </c>
+      <c r="F138" t="s">
+        <v>725</v>
+      </c>
+      <c r="G138" t="s">
+        <v>666</v>
+      </c>
+      <c r="H138" t="s">
+        <v>1150</v>
+      </c>
+      <c r="I138" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J138" t="s">
+        <v>1151</v>
+      </c>
+      <c r="K138" t="s">
+        <v>1152</v>
+      </c>
+      <c r="L138" t="s">
+        <v>1153</v>
+      </c>
+      <c r="M138" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C139" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D139" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E139" s="3">
+        <v>46160</v>
+      </c>
+      <c r="F139" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G139" t="s">
+        <v>666</v>
+      </c>
+      <c r="H139" t="s">
+        <v>1160</v>
+      </c>
+      <c r="I139" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J139" t="s">
+        <v>1161</v>
+      </c>
+      <c r="K139" t="s">
+        <v>1162</v>
+      </c>
+      <c r="L139" t="s">
+        <v>1163</v>
+      </c>
+      <c r="M139" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C140" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D140" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E140" s="3">
+        <v>46160</v>
+      </c>
+      <c r="F140" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G140" t="s">
+        <v>666</v>
+      </c>
+      <c r="H140" t="s">
+        <v>1167</v>
+      </c>
+      <c r="I140" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J140" t="s">
+        <v>1168</v>
+      </c>
+      <c r="K140" t="s">
+        <v>1169</v>
+      </c>
+      <c r="L140" t="s">
+        <v>1170</v>
+      </c>
+      <c r="M140" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C141" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D141" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E141" s="3">
+        <v>46232</v>
+      </c>
+      <c r="F141" t="s">
+        <v>824</v>
+      </c>
+      <c r="G141" t="s">
+        <v>1176</v>
+      </c>
+      <c r="H141" t="s">
+        <v>666</v>
+      </c>
+      <c r="I141" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J141" t="s">
+        <v>1177</v>
+      </c>
+      <c r="K141" t="s">
+        <v>1178</v>
+      </c>
+      <c r="L141" t="s">
+        <v>1179</v>
+      </c>
+      <c r="M141" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B142" t="s">
+        <v>385</v>
+      </c>
+      <c r="C142" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D142" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E142" s="3">
+        <v>46159</v>
+      </c>
+      <c r="F142" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G142" t="s">
+        <v>1182</v>
+      </c>
+      <c r="H142" t="s">
+        <v>666</v>
+      </c>
+      <c r="I142" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J142" t="s">
+        <v>1183</v>
+      </c>
+      <c r="K142" t="s">
+        <v>1184</v>
+      </c>
+      <c r="L142" t="s">
+        <v>1185</v>
+      </c>
+      <c r="M142" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C143" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D143" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E143" s="3">
         <v>46203</v>
       </c>
-      <c r="F117" t="s">
-        <v>980</v>
-      </c>
-      <c r="G117" t="s">
-        <v>667</v>
-      </c>
-      <c r="H117" t="s">
-        <v>981</v>
-      </c>
-      <c r="I117" t="s">
-        <v>885</v>
-      </c>
-      <c r="J117" t="s">
-        <v>982</v>
-      </c>
-      <c r="K117" t="s">
-        <v>983</v>
-      </c>
-      <c r="L117" t="s">
-        <v>984</v>
-      </c>
-      <c r="M117" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>996</v>
-      </c>
-      <c r="B118" t="s">
-        <v>987</v>
-      </c>
-      <c r="C118" t="s">
-        <v>988</v>
-      </c>
-      <c r="D118" t="s">
+      <c r="F143" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G143" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H143" t="s">
+        <v>666</v>
+      </c>
+      <c r="I143" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J143" t="s">
+        <v>1193</v>
+      </c>
+      <c r="K143" t="s">
+        <v>1194</v>
+      </c>
+      <c r="L143" t="s">
+        <v>1195</v>
+      </c>
+      <c r="M143" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C144" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D144" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E144" s="3">
+        <v>46164</v>
+      </c>
+      <c r="F144" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G144" t="s">
+        <v>1202</v>
+      </c>
+      <c r="H144" t="s">
+        <v>1203</v>
+      </c>
+      <c r="I144" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J144" t="s">
+        <v>1204</v>
+      </c>
+      <c r="K144" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L144" t="s">
+        <v>1206</v>
+      </c>
+      <c r="M144" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B145" t="s">
+        <v>328</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D145" t="s">
+        <v>208</v>
+      </c>
+      <c r="E145" s="3">
+        <v>46157</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G145" t="s">
+        <v>1210</v>
+      </c>
+      <c r="H145" t="s">
+        <v>1203</v>
+      </c>
+      <c r="I145" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J145" t="s">
+        <v>1212</v>
+      </c>
+      <c r="K145" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L145" t="s">
+        <v>1214</v>
+      </c>
+      <c r="M145" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D146" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E146" s="3">
+        <v>46176</v>
+      </c>
+      <c r="F146" t="s">
+        <v>694</v>
+      </c>
+      <c r="G146" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H146" t="s">
+        <v>1203</v>
+      </c>
+      <c r="I146" t="s">
+        <v>1221</v>
+      </c>
+      <c r="J146" t="s">
+        <v>1222</v>
+      </c>
+      <c r="K146" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L146" t="s">
+        <v>1224</v>
+      </c>
+      <c r="M146" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C147" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D147" t="s">
+        <v>272</v>
+      </c>
+      <c r="E147" s="3">
+        <v>46180</v>
+      </c>
+      <c r="F147" t="s">
         <v>725</v>
       </c>
-      <c r="E118" s="3">
-        <v>46146</v>
-      </c>
-      <c r="F118" t="s">
-        <v>989</v>
-      </c>
-      <c r="G118" t="s">
-        <v>990</v>
-      </c>
-      <c r="H118" t="s">
-        <v>991</v>
-      </c>
-      <c r="I118" t="s">
-        <v>885</v>
-      </c>
-      <c r="J118" t="s">
-        <v>995</v>
-      </c>
-      <c r="K118" t="s">
-        <v>992</v>
-      </c>
-      <c r="L118" t="s">
-        <v>993</v>
-      </c>
-      <c r="M118" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>1006</v>
-      </c>
-      <c r="B119" t="s">
-        <v>997</v>
-      </c>
-      <c r="C119" t="s">
-        <v>998</v>
-      </c>
-      <c r="D119" t="s">
-        <v>999</v>
-      </c>
-      <c r="E119" s="3">
-        <v>46220</v>
-      </c>
-      <c r="F119" t="s">
-        <v>1000</v>
-      </c>
-      <c r="G119" t="s">
-        <v>667</v>
-      </c>
-      <c r="H119" t="s">
-        <v>1001</v>
-      </c>
-      <c r="I119" t="s">
-        <v>885</v>
-      </c>
-      <c r="J119" t="s">
-        <v>1002</v>
-      </c>
-      <c r="K119" t="s">
-        <v>1003</v>
-      </c>
-      <c r="L119" t="s">
-        <v>1004</v>
-      </c>
-      <c r="M119" t="s">
-        <v>1005</v>
+      <c r="G147" t="s">
+        <v>1228</v>
+      </c>
+      <c r="H147" t="s">
+        <v>1203</v>
+      </c>
+      <c r="I147" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J147" t="s">
+        <v>1229</v>
+      </c>
+      <c r="K147" t="s">
+        <v>1230</v>
+      </c>
+      <c r="L147" t="s">
+        <v>1231</v>
+      </c>
+      <c r="M147" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B148" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C148" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D148" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E148" s="3">
+        <v>46193</v>
+      </c>
+      <c r="F148" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G148" t="s">
+        <v>1238</v>
+      </c>
+      <c r="H148" t="s">
+        <v>1203</v>
+      </c>
+      <c r="I148" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J148" t="s">
+        <v>1239</v>
+      </c>
+      <c r="K148" t="s">
+        <v>1240</v>
+      </c>
+      <c r="L148" t="s">
+        <v>1241</v>
+      </c>
+      <c r="M148" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B149" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D149" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E149" s="3">
+        <v>46193</v>
+      </c>
+      <c r="F149" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G149" t="s">
+        <v>1245</v>
+      </c>
+      <c r="H149" t="s">
+        <v>1203</v>
+      </c>
+      <c r="I149" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J149" t="s">
+        <v>1246</v>
+      </c>
+      <c r="K149" t="s">
+        <v>1247</v>
+      </c>
+      <c r="L149" t="s">
+        <v>1248</v>
+      </c>
+      <c r="M149" t="s">
+        <v>1249</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N103">
-    <sortCondition ref="B1:B103"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N126">
+    <sortCondition ref="C1:C126"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F145" r:id="rId1" xr:uid="{AF385F1D-8423-4CF2-9485-1A010374DA01}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>